--- a/Modelos IA/comparacion_predicciones.xlsx
+++ b/Modelos IA/comparacion_predicciones.xlsx
@@ -459,7 +459,7 @@
         <v>461</v>
       </c>
       <c r="C3" t="n">
-        <v>384.4809958661891</v>
+        <v>384.4809958661889</v>
       </c>
     </row>
     <row r="4">
@@ -470,7 +470,7 @@
         <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>409.5848118059489</v>
+        <v>409.5848118059488</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>302.0641381787786</v>
+        <v>302.0641381787785</v>
       </c>
     </row>
     <row r="8">
@@ -602,7 +602,7 @@
         <v>165</v>
       </c>
       <c r="C16" t="n">
-        <v>156.5349444651627</v>
+        <v>156.5349444651628</v>
       </c>
     </row>
     <row r="17">
@@ -635,7 +635,7 @@
         <v>298</v>
       </c>
       <c r="C19" t="n">
-        <v>329.1566816203824</v>
+        <v>329.1566816203823</v>
       </c>
     </row>
     <row r="20">
@@ -646,7 +646,7 @@
         <v>328</v>
       </c>
       <c r="C20" t="n">
-        <v>342.7043933728977</v>
+        <v>342.7043933728978</v>
       </c>
     </row>
     <row r="21">
@@ -701,7 +701,7 @@
         <v>329</v>
       </c>
       <c r="C25" t="n">
-        <v>315.8803144935424</v>
+        <v>315.8803144935423</v>
       </c>
     </row>
     <row r="26">
@@ -712,7 +712,7 @@
         <v>323</v>
       </c>
       <c r="C26" t="n">
-        <v>340.297201658326</v>
+        <v>340.2972016583261</v>
       </c>
     </row>
     <row r="27">
@@ -756,7 +756,7 @@
         <v>245</v>
       </c>
       <c r="C30" t="n">
-        <v>251.4263003671176</v>
+        <v>251.4263003671177</v>
       </c>
     </row>
     <row r="31">
@@ -800,7 +800,7 @@
         <v>89</v>
       </c>
       <c r="C34" t="n">
-        <v>90.25531809412118</v>
+        <v>90.25531809412115</v>
       </c>
     </row>
     <row r="35">
@@ -811,7 +811,7 @@
         <v>65</v>
       </c>
       <c r="C35" t="n">
-        <v>86.45451244537014</v>
+        <v>86.45451244537013</v>
       </c>
     </row>
     <row r="36">
@@ -866,7 +866,7 @@
         <v>378</v>
       </c>
       <c r="C40" t="n">
-        <v>412.1409890011336</v>
+        <v>412.1409890011337</v>
       </c>
     </row>
     <row r="41">
@@ -954,7 +954,7 @@
         <v>337</v>
       </c>
       <c r="C48" t="n">
-        <v>351.7538068993896</v>
+        <v>351.7538068993897</v>
       </c>
     </row>
     <row r="49">
@@ -976,7 +976,7 @@
         <v>357</v>
       </c>
       <c r="C50" t="n">
-        <v>346.3536729712842</v>
+        <v>346.3536729712843</v>
       </c>
     </row>
     <row r="51">
@@ -998,7 +998,7 @@
         <v>344</v>
       </c>
       <c r="C52" t="n">
-        <v>334.0643009458739</v>
+        <v>334.064300945874</v>
       </c>
     </row>
     <row r="53">
@@ -1031,7 +1031,7 @@
         <v>177</v>
       </c>
       <c r="C55" t="n">
-        <v>194.189047478389</v>
+        <v>194.1890474783889</v>
       </c>
     </row>
     <row r="56">
@@ -1086,7 +1086,7 @@
         <v>54</v>
       </c>
       <c r="C60" t="n">
-        <v>91.1354872013209</v>
+        <v>91.13548720132088</v>
       </c>
     </row>
     <row r="61">
@@ -1097,7 +1097,7 @@
         <v>106</v>
       </c>
       <c r="C61" t="n">
-        <v>150.5039709021086</v>
+        <v>150.5039709021085</v>
       </c>
     </row>
     <row r="62">
@@ -1108,7 +1108,7 @@
         <v>239</v>
       </c>
       <c r="C62" t="n">
-        <v>363.136256564958</v>
+        <v>363.1362565649579</v>
       </c>
     </row>
     <row r="63">
@@ -1130,7 +1130,7 @@
         <v>392</v>
       </c>
       <c r="C64" t="n">
-        <v>419.560239214651</v>
+        <v>419.5602392146509</v>
       </c>
     </row>
     <row r="65">
@@ -1163,7 +1163,7 @@
         <v>419</v>
       </c>
       <c r="C67" t="n">
-        <v>421.5045143393205</v>
+        <v>421.5045143393204</v>
       </c>
     </row>
     <row r="68">
@@ -1240,7 +1240,7 @@
         <v>447</v>
       </c>
       <c r="C74" t="n">
-        <v>376.1403833386153</v>
+        <v>376.1403833386154</v>
       </c>
     </row>
     <row r="75">
@@ -1339,7 +1339,7 @@
         <v>94</v>
       </c>
       <c r="C83" t="n">
-        <v>103.0922694197296</v>
+        <v>103.0922694197297</v>
       </c>
     </row>
     <row r="84">
@@ -1361,7 +1361,7 @@
         <v>137</v>
       </c>
       <c r="C85" t="n">
-        <v>144.810374781561</v>
+        <v>144.8103747815611</v>
       </c>
     </row>
     <row r="86">
@@ -1427,7 +1427,7 @@
         <v>372</v>
       </c>
       <c r="C91" t="n">
-        <v>405.2866447146979</v>
+        <v>405.286644714698</v>
       </c>
     </row>
     <row r="92">
@@ -1449,7 +1449,7 @@
         <v>352</v>
       </c>
       <c r="C93" t="n">
-        <v>355.6567219438389</v>
+        <v>355.6567219438391</v>
       </c>
     </row>
     <row r="94">
@@ -1482,7 +1482,7 @@
         <v>363</v>
       </c>
       <c r="C96" t="n">
-        <v>336.2354896205314</v>
+        <v>336.2354896205313</v>
       </c>
     </row>
     <row r="97">
@@ -1504,7 +1504,7 @@
         <v>400</v>
       </c>
       <c r="C98" t="n">
-        <v>370.2805857954532</v>
+        <v>370.2805857954531</v>
       </c>
     </row>
     <row r="99">
@@ -1691,7 +1691,7 @@
         <v>322</v>
       </c>
       <c r="C115" t="n">
-        <v>325.7119349101881</v>
+        <v>325.711934910188</v>
       </c>
     </row>
     <row r="116">
@@ -1735,7 +1735,7 @@
         <v>293</v>
       </c>
       <c r="C119" t="n">
-        <v>308.567248805163</v>
+        <v>308.5672488051629</v>
       </c>
     </row>
     <row r="120">
@@ -1768,7 +1768,7 @@
         <v>394</v>
       </c>
       <c r="C122" t="n">
-        <v>337.503476759359</v>
+        <v>337.5034767593591</v>
       </c>
     </row>
     <row r="123">
@@ -1867,7 +1867,7 @@
         <v>74</v>
       </c>
       <c r="C131" t="n">
-        <v>86.62427930453181</v>
+        <v>86.6242793045318</v>
       </c>
     </row>
     <row r="132">
@@ -1900,7 +1900,7 @@
         <v>228</v>
       </c>
       <c r="C134" t="n">
-        <v>382.6623539611978</v>
+        <v>382.6623539611977</v>
       </c>
     </row>
     <row r="135">
@@ -1922,7 +1922,7 @@
         <v>351</v>
       </c>
       <c r="C136" t="n">
-        <v>412.7566391702759</v>
+        <v>412.756639170276</v>
       </c>
     </row>
     <row r="137">
@@ -1977,7 +1977,7 @@
         <v>377</v>
       </c>
       <c r="C141" t="n">
-        <v>408.9962706822193</v>
+        <v>408.9962706822192</v>
       </c>
     </row>
     <row r="142">
@@ -2043,7 +2043,7 @@
         <v>359</v>
       </c>
       <c r="C147" t="n">
-        <v>354.9392938498606</v>
+        <v>354.9392938498607</v>
       </c>
     </row>
     <row r="148">
@@ -2054,7 +2054,7 @@
         <v>323</v>
       </c>
       <c r="C148" t="n">
-        <v>342.4269452566568</v>
+        <v>342.4269452566569</v>
       </c>
     </row>
     <row r="149">
@@ -2087,7 +2087,7 @@
         <v>162</v>
       </c>
       <c r="C151" t="n">
-        <v>180.5601124631596</v>
+        <v>180.5601124631597</v>
       </c>
     </row>
     <row r="152">
@@ -2098,7 +2098,7 @@
         <v>136</v>
       </c>
       <c r="C152" t="n">
-        <v>125.3418909998175</v>
+        <v>125.3418909998176</v>
       </c>
     </row>
     <row r="153">
@@ -2175,7 +2175,7 @@
         <v>392</v>
       </c>
       <c r="C159" t="n">
-        <v>357.4006013047684</v>
+        <v>357.4006013047683</v>
       </c>
     </row>
     <row r="160">
@@ -2252,7 +2252,7 @@
         <v>338</v>
       </c>
       <c r="C166" t="n">
-        <v>372.410528117049</v>
+        <v>372.4105281170489</v>
       </c>
     </row>
     <row r="167">
@@ -2285,7 +2285,7 @@
         <v>365</v>
       </c>
       <c r="C169" t="n">
-        <v>388.9478151597679</v>
+        <v>388.9478151597678</v>
       </c>
     </row>
     <row r="170">
@@ -2461,7 +2461,7 @@
         <v>419</v>
       </c>
       <c r="C185" t="n">
-        <v>408.9466854174334</v>
+        <v>408.9466854174333</v>
       </c>
     </row>
     <row r="186">
@@ -2516,7 +2516,7 @@
         <v>314</v>
       </c>
       <c r="C190" t="n">
-        <v>374.294620067713</v>
+        <v>374.2946200677129</v>
       </c>
     </row>
     <row r="191">
@@ -2527,7 +2527,7 @@
         <v>331</v>
       </c>
       <c r="C191" t="n">
-        <v>366.325338296861</v>
+        <v>366.3253382968611</v>
       </c>
     </row>
     <row r="192">
@@ -2538,7 +2538,7 @@
         <v>368</v>
       </c>
       <c r="C192" t="n">
-        <v>388.6609294434523</v>
+        <v>388.6609294434522</v>
       </c>
     </row>
     <row r="193">
@@ -2582,7 +2582,7 @@
         <v>356</v>
       </c>
       <c r="C196" t="n">
-        <v>396.4142542939558</v>
+        <v>396.4142542939557</v>
       </c>
     </row>
     <row r="197">
@@ -2604,7 +2604,7 @@
         <v>268</v>
       </c>
       <c r="C198" t="n">
-        <v>278.2329031741886</v>
+        <v>278.2329031741885</v>
       </c>
     </row>
     <row r="199">
@@ -2659,7 +2659,7 @@
         <v>151</v>
       </c>
       <c r="C203" t="n">
-        <v>137.4822609934629</v>
+        <v>137.4822609934628</v>
       </c>
     </row>
     <row r="204">
@@ -2670,7 +2670,7 @@
         <v>139</v>
       </c>
       <c r="C204" t="n">
-        <v>130.06078276997</v>
+        <v>130.0607827699701</v>
       </c>
     </row>
     <row r="205">
@@ -2692,7 +2692,7 @@
         <v>221</v>
       </c>
       <c r="C206" t="n">
-        <v>293.2125447434882</v>
+        <v>293.2125447434883</v>
       </c>
     </row>
     <row r="207">
@@ -2791,7 +2791,7 @@
         <v>325</v>
       </c>
       <c r="C215" t="n">
-        <v>356.4579883794788</v>
+        <v>356.4579883794789</v>
       </c>
     </row>
     <row r="216">
@@ -2802,7 +2802,7 @@
         <v>370</v>
       </c>
       <c r="C216" t="n">
-        <v>349.3758188342237</v>
+        <v>349.3758188342238</v>
       </c>
     </row>
     <row r="217">
@@ -2846,7 +2846,7 @@
         <v>467</v>
       </c>
       <c r="C220" t="n">
-        <v>412.3909164182441</v>
+        <v>412.390916418244</v>
       </c>
     </row>
     <row r="221">
@@ -2857,7 +2857,7 @@
         <v>355</v>
       </c>
       <c r="C221" t="n">
-        <v>414.1526952422221</v>
+        <v>414.1526952422222</v>
       </c>
     </row>
     <row r="222">
@@ -2879,7 +2879,7 @@
         <v>250</v>
       </c>
       <c r="C223" t="n">
-        <v>291.9372046969436</v>
+        <v>291.9372046969435</v>
       </c>
     </row>
     <row r="224">
@@ -3011,7 +3011,7 @@
         <v>343</v>
       </c>
       <c r="C235" t="n">
-        <v>345.4917848522309</v>
+        <v>345.491784852231</v>
       </c>
     </row>
     <row r="236">
@@ -3099,7 +3099,7 @@
         <v>393</v>
       </c>
       <c r="C243" t="n">
-        <v>393.9972435529237</v>
+        <v>393.9972435529238</v>
       </c>
     </row>
     <row r="244">
@@ -3110,7 +3110,7 @@
         <v>316</v>
       </c>
       <c r="C244" t="n">
-        <v>365.5031270800064</v>
+        <v>365.5031270800063</v>
       </c>
     </row>
     <row r="245">
@@ -3297,7 +3297,7 @@
         <v>363</v>
       </c>
       <c r="C261" t="n">
-        <v>411.2920079713167</v>
+        <v>411.2920079713168</v>
       </c>
     </row>
     <row r="262">
@@ -3374,7 +3374,7 @@
         <v>319</v>
       </c>
       <c r="C268" t="n">
-        <v>362.3271310884686</v>
+        <v>362.3271310884687</v>
       </c>
     </row>
     <row r="269">
@@ -3451,7 +3451,7 @@
         <v>78</v>
       </c>
       <c r="C275" t="n">
-        <v>86.84189297127966</v>
+        <v>86.84189297127969</v>
       </c>
     </row>
     <row r="276">
@@ -3517,7 +3517,7 @@
         <v>445</v>
       </c>
       <c r="C281" t="n">
-        <v>455.0748865540118</v>
+        <v>455.0748865540119</v>
       </c>
     </row>
     <row r="282">
@@ -3539,7 +3539,7 @@
         <v>476</v>
       </c>
       <c r="C283" t="n">
-        <v>483.2786928256571</v>
+        <v>483.2786928256572</v>
       </c>
     </row>
     <row r="284">
@@ -3803,7 +3803,7 @@
         <v>441</v>
       </c>
       <c r="C307" t="n">
-        <v>439.0431753808775</v>
+        <v>439.0431753808776</v>
       </c>
     </row>
     <row r="308">
@@ -3814,7 +3814,7 @@
         <v>441</v>
       </c>
       <c r="C308" t="n">
-        <v>437.3906185036522</v>
+        <v>437.3906185036523</v>
       </c>
     </row>
     <row r="309">
@@ -3825,7 +3825,7 @@
         <v>397</v>
       </c>
       <c r="C309" t="n">
-        <v>437.2964254700602</v>
+        <v>437.2964254700603</v>
       </c>
     </row>
     <row r="310">
@@ -3924,7 +3924,7 @@
         <v>263</v>
       </c>
       <c r="C318" t="n">
-        <v>289.2219650657691</v>
+        <v>289.221965065769</v>
       </c>
     </row>
     <row r="319">
@@ -4012,7 +4012,7 @@
         <v>218</v>
       </c>
       <c r="C326" t="n">
-        <v>305.1953340581048</v>
+        <v>305.1953340581047</v>
       </c>
     </row>
     <row r="327">
@@ -4023,7 +4023,7 @@
         <v>354</v>
       </c>
       <c r="C327" t="n">
-        <v>338.8220529591562</v>
+        <v>338.8220529591561</v>
       </c>
     </row>
     <row r="328">
@@ -4089,7 +4089,7 @@
         <v>411</v>
       </c>
       <c r="C333" t="n">
-        <v>428.2975614895914</v>
+        <v>428.2975614895915</v>
       </c>
     </row>
     <row r="334">
@@ -4122,7 +4122,7 @@
         <v>372</v>
       </c>
       <c r="C336" t="n">
-        <v>399.0153456966284</v>
+        <v>399.0153456966285</v>
       </c>
     </row>
     <row r="337">
@@ -4144,7 +4144,7 @@
         <v>454</v>
       </c>
       <c r="C338" t="n">
-        <v>423.1510765907439</v>
+        <v>423.1510765907437</v>
       </c>
     </row>
     <row r="339">
@@ -4155,7 +4155,7 @@
         <v>520</v>
       </c>
       <c r="C339" t="n">
-        <v>439.1126647408986</v>
+        <v>439.1126647408987</v>
       </c>
     </row>
     <row r="340">
@@ -4177,7 +4177,7 @@
         <v>318</v>
       </c>
       <c r="C341" t="n">
-        <v>392.0872463720853</v>
+        <v>392.0872463720854</v>
       </c>
     </row>
     <row r="342">
@@ -4210,7 +4210,7 @@
         <v>323</v>
       </c>
       <c r="C344" t="n">
-        <v>266.0244739702761</v>
+        <v>266.0244739702762</v>
       </c>
     </row>
     <row r="345">
@@ -4243,7 +4243,7 @@
         <v>145</v>
       </c>
       <c r="C347" t="n">
-        <v>159.2801080798807</v>
+        <v>159.2801080798808</v>
       </c>
     </row>
     <row r="348">
@@ -4309,7 +4309,7 @@
         <v>245</v>
       </c>
       <c r="C353" t="n">
-        <v>243.8147901225333</v>
+        <v>243.8147901225332</v>
       </c>
     </row>
     <row r="354">
@@ -4441,7 +4441,7 @@
         <v>296</v>
       </c>
       <c r="C365" t="n">
-        <v>339.8579828739145</v>
+        <v>339.8579828739146</v>
       </c>
     </row>
     <row r="366">
@@ -4452,7 +4452,7 @@
         <v>258</v>
       </c>
       <c r="C366" t="n">
-        <v>281.6766554824962</v>
+        <v>281.6766554824963</v>
       </c>
     </row>
     <row r="367">
@@ -4507,7 +4507,7 @@
         <v>85</v>
       </c>
       <c r="C371" t="n">
-        <v>87.06271460122112</v>
+        <v>87.0627146012211</v>
       </c>
     </row>
     <row r="372">
@@ -4584,7 +4584,7 @@
         <v>517</v>
       </c>
       <c r="C378" t="n">
-        <v>539.7785878838189</v>
+        <v>539.778587883819</v>
       </c>
     </row>
     <row r="379">
@@ -4661,7 +4661,7 @@
         <v>445</v>
       </c>
       <c r="C385" t="n">
-        <v>468.4535511387879</v>
+        <v>468.4535511387878</v>
       </c>
     </row>
     <row r="386">
@@ -4694,7 +4694,7 @@
         <v>398</v>
       </c>
       <c r="C388" t="n">
-        <v>402.0974832902123</v>
+        <v>402.0974832902124</v>
       </c>
     </row>
     <row r="389">
@@ -4771,7 +4771,7 @@
         <v>137</v>
       </c>
       <c r="C395" t="n">
-        <v>88.59113129699179</v>
+        <v>88.5911312969918</v>
       </c>
     </row>
     <row r="396">
@@ -4870,7 +4870,7 @@
         <v>543</v>
       </c>
       <c r="C404" t="n">
-        <v>563.6463947961771</v>
+        <v>563.646394796177</v>
       </c>
     </row>
     <row r="405">
@@ -4903,7 +4903,7 @@
         <v>473</v>
       </c>
       <c r="C407" t="n">
-        <v>452.8307397973193</v>
+        <v>452.8307397973194</v>
       </c>
     </row>
     <row r="408">
@@ -4914,7 +4914,7 @@
         <v>455</v>
       </c>
       <c r="C408" t="n">
-        <v>480.0157950948907</v>
+        <v>480.0157950948906</v>
       </c>
     </row>
     <row r="409">
@@ -4947,7 +4947,7 @@
         <v>474</v>
       </c>
       <c r="C411" t="n">
-        <v>516.2418667033623</v>
+        <v>516.2418667033622</v>
       </c>
     </row>
     <row r="412">
@@ -4969,7 +4969,7 @@
         <v>357</v>
       </c>
       <c r="C413" t="n">
-        <v>338.5382353618861</v>
+        <v>338.5382353618862</v>
       </c>
     </row>
     <row r="414">
@@ -5101,7 +5101,7 @@
         <v>549</v>
       </c>
       <c r="C425" t="n">
-        <v>584.0777967737077</v>
+        <v>584.0777967737076</v>
       </c>
     </row>
     <row r="426">
@@ -5112,7 +5112,7 @@
         <v>530</v>
       </c>
       <c r="C426" t="n">
-        <v>553.5224764768267</v>
+        <v>553.5224764768268</v>
       </c>
     </row>
     <row r="427">
@@ -5123,7 +5123,7 @@
         <v>574</v>
       </c>
       <c r="C427" t="n">
-        <v>523.2362046756483</v>
+        <v>523.2362046756482</v>
       </c>
     </row>
     <row r="428">
@@ -5387,7 +5387,7 @@
         <v>573</v>
       </c>
       <c r="C451" t="n">
-        <v>529.1055921723871</v>
+        <v>529.1055921723872</v>
       </c>
     </row>
     <row r="452">
@@ -5409,7 +5409,7 @@
         <v>453</v>
       </c>
       <c r="C453" t="n">
-        <v>490.2105533137168</v>
+        <v>490.2105533137169</v>
       </c>
     </row>
     <row r="454">
@@ -5453,7 +5453,7 @@
         <v>486</v>
       </c>
       <c r="C457" t="n">
-        <v>481.535812985472</v>
+        <v>481.5358129854719</v>
       </c>
     </row>
     <row r="458">
@@ -5486,7 +5486,7 @@
         <v>552</v>
       </c>
       <c r="C460" t="n">
-        <v>546.6546653152104</v>
+        <v>546.6546653152105</v>
       </c>
     </row>
     <row r="461">
@@ -5519,7 +5519,7 @@
         <v>344</v>
       </c>
       <c r="C463" t="n">
-        <v>357.180241874598</v>
+        <v>357.1802418745981</v>
       </c>
     </row>
     <row r="464">
@@ -5530,7 +5530,7 @@
         <v>376</v>
       </c>
       <c r="C464" t="n">
-        <v>346.6746996588195</v>
+        <v>346.6746996588196</v>
       </c>
     </row>
     <row r="465">
@@ -5706,7 +5706,7 @@
         <v>516</v>
       </c>
       <c r="C480" t="n">
-        <v>424.8631271980518</v>
+        <v>424.8631271980519</v>
       </c>
     </row>
     <row r="481">
@@ -5717,7 +5717,7 @@
         <v>449</v>
       </c>
       <c r="C481" t="n">
-        <v>520.9270429944211</v>
+        <v>520.9270429944212</v>
       </c>
     </row>
     <row r="482">
@@ -5761,7 +5761,7 @@
         <v>344</v>
       </c>
       <c r="C485" t="n">
-        <v>417.2045766136929</v>
+        <v>417.2045766136928</v>
       </c>
     </row>
     <row r="486">
@@ -5794,7 +5794,7 @@
         <v>333</v>
       </c>
       <c r="C488" t="n">
-        <v>243.1216746281154</v>
+        <v>243.1216746281153</v>
       </c>
     </row>
     <row r="489">
@@ -5849,7 +5849,7 @@
         <v>233</v>
       </c>
       <c r="C493" t="n">
-        <v>520.0618331646056</v>
+        <v>520.0618331646057</v>
       </c>
     </row>
     <row r="494">
@@ -5904,7 +5904,7 @@
         <v>309</v>
       </c>
       <c r="C498" t="n">
-        <v>171.3762352369691</v>
+        <v>171.3762352369692</v>
       </c>
     </row>
     <row r="499">
@@ -5948,7 +5948,7 @@
         <v>446</v>
       </c>
       <c r="C502" t="n">
-        <v>463.2486738056887</v>
+        <v>463.2486738056888</v>
       </c>
     </row>
     <row r="503">
@@ -6036,7 +6036,7 @@
         <v>301</v>
       </c>
       <c r="C510" t="n">
-        <v>297.41947157572</v>
+        <v>297.4194715757201</v>
       </c>
     </row>
     <row r="511">
@@ -6157,7 +6157,7 @@
         <v>618</v>
       </c>
       <c r="C521" t="n">
-        <v>603.3182361894387</v>
+        <v>603.3182361894386</v>
       </c>
     </row>
     <row r="522">
@@ -6168,7 +6168,7 @@
         <v>674</v>
       </c>
       <c r="C522" t="n">
-        <v>579.8690637211392</v>
+        <v>579.8690637211391</v>
       </c>
     </row>
     <row r="523">
@@ -6245,7 +6245,7 @@
         <v>467</v>
       </c>
       <c r="C529" t="n">
-        <v>459.9157015367794</v>
+        <v>459.9157015367793</v>
       </c>
     </row>
     <row r="530">
@@ -6267,7 +6267,7 @@
         <v>466</v>
       </c>
       <c r="C531" t="n">
-        <v>506.4521168017186</v>
+        <v>506.4521168017185</v>
       </c>
     </row>
     <row r="532">
@@ -6366,7 +6366,7 @@
         <v>185</v>
       </c>
       <c r="C540" t="n">
-        <v>185.6503154252737</v>
+        <v>185.6503154252738</v>
       </c>
     </row>
     <row r="541">
@@ -6388,7 +6388,7 @@
         <v>308</v>
       </c>
       <c r="C542" t="n">
-        <v>316.5679613647842</v>
+        <v>316.5679613647841</v>
       </c>
     </row>
     <row r="543">
@@ -6410,7 +6410,7 @@
         <v>613</v>
       </c>
       <c r="C544" t="n">
-        <v>576.5489541868167</v>
+        <v>576.5489541868166</v>
       </c>
     </row>
     <row r="545">
@@ -6432,7 +6432,7 @@
         <v>604</v>
       </c>
       <c r="C546" t="n">
-        <v>595.6181084343663</v>
+        <v>595.6181084343661</v>
       </c>
     </row>
     <row r="547">
@@ -6509,7 +6509,7 @@
         <v>511</v>
       </c>
       <c r="C553" t="n">
-        <v>488.5001413852604</v>
+        <v>488.5001413852603</v>
       </c>
     </row>
     <row r="554">
@@ -6520,7 +6520,7 @@
         <v>696</v>
       </c>
       <c r="C554" t="n">
-        <v>514.4616376529822</v>
+        <v>514.4616376529821</v>
       </c>
     </row>
     <row r="555">
@@ -6531,7 +6531,7 @@
         <v>600</v>
       </c>
       <c r="C555" t="n">
-        <v>606.7309546364725</v>
+        <v>606.7309546364723</v>
       </c>
     </row>
     <row r="556">
@@ -6553,7 +6553,7 @@
         <v>379</v>
       </c>
       <c r="C557" t="n">
-        <v>432.0949165119641</v>
+        <v>432.094916511964</v>
       </c>
     </row>
     <row r="558">
@@ -6564,7 +6564,7 @@
         <v>358</v>
       </c>
       <c r="C558" t="n">
-        <v>365.0720363295378</v>
+        <v>365.0720363295376</v>
       </c>
     </row>
     <row r="559">
@@ -6674,7 +6674,7 @@
         <v>523</v>
       </c>
       <c r="C568" t="n">
-        <v>526.9087044804975</v>
+        <v>526.9087044804974</v>
       </c>
     </row>
     <row r="569">
@@ -6685,7 +6685,7 @@
         <v>540</v>
       </c>
       <c r="C569" t="n">
-        <v>539.4390862238216</v>
+        <v>539.4390862238215</v>
       </c>
     </row>
     <row r="570">
@@ -6696,7 +6696,7 @@
         <v>527</v>
       </c>
       <c r="C570" t="n">
-        <v>531.4544673880725</v>
+        <v>531.4544673880728</v>
       </c>
     </row>
     <row r="571">
@@ -6718,7 +6718,7 @@
         <v>527</v>
       </c>
       <c r="C572" t="n">
-        <v>514.0327327417926</v>
+        <v>514.0327327417928</v>
       </c>
     </row>
     <row r="573">
@@ -6729,7 +6729,7 @@
         <v>452</v>
       </c>
       <c r="C573" t="n">
-        <v>504.7632903504332</v>
+        <v>504.7632903504333</v>
       </c>
     </row>
     <row r="574">
@@ -6751,7 +6751,7 @@
         <v>444</v>
       </c>
       <c r="C575" t="n">
-        <v>443.9359977748955</v>
+        <v>443.9359977748956</v>
       </c>
     </row>
     <row r="576">
@@ -6795,7 +6795,7 @@
         <v>650</v>
       </c>
       <c r="C579" t="n">
-        <v>550.918816896266</v>
+        <v>550.9188168962661</v>
       </c>
     </row>
     <row r="580">
@@ -6828,7 +6828,7 @@
         <v>375</v>
       </c>
       <c r="C582" t="n">
-        <v>410.9259406456467</v>
+        <v>410.9259406456468</v>
       </c>
     </row>
     <row r="583">
@@ -6993,7 +6993,7 @@
         <v>440</v>
       </c>
       <c r="C597" t="n">
-        <v>318.6576789333531</v>
+        <v>318.657678933353</v>
       </c>
     </row>
     <row r="598">
@@ -7026,7 +7026,7 @@
         <v>516</v>
       </c>
       <c r="C600" t="n">
-        <v>408.1189600631111</v>
+        <v>408.1189600631112</v>
       </c>
     </row>
     <row r="601">
@@ -7202,7 +7202,7 @@
         <v>630</v>
       </c>
       <c r="C616" t="n">
-        <v>549.155558138746</v>
+        <v>549.1555581387461</v>
       </c>
     </row>
     <row r="617">
@@ -7224,7 +7224,7 @@
         <v>538</v>
       </c>
       <c r="C618" t="n">
-        <v>579.0199882910176</v>
+        <v>579.0199882910177</v>
       </c>
     </row>
     <row r="619">
@@ -7246,7 +7246,7 @@
         <v>541</v>
       </c>
       <c r="C620" t="n">
-        <v>533.3745013408092</v>
+        <v>533.374501340809</v>
       </c>
     </row>
     <row r="621">
@@ -7301,7 +7301,7 @@
         <v>462</v>
       </c>
       <c r="C625" t="n">
-        <v>462.5826049485448</v>
+        <v>462.5826049485447</v>
       </c>
     </row>
     <row r="626">
@@ -7323,7 +7323,7 @@
         <v>435</v>
       </c>
       <c r="C627" t="n">
-        <v>457.7835968852248</v>
+        <v>457.7835968852247</v>
       </c>
     </row>
     <row r="628">
@@ -7345,7 +7345,7 @@
         <v>358</v>
       </c>
       <c r="C629" t="n">
-        <v>339.7812072378598</v>
+        <v>339.7812072378599</v>
       </c>
     </row>
     <row r="630">
@@ -7400,7 +7400,7 @@
         <v>156</v>
       </c>
       <c r="C634" t="n">
-        <v>159.2755745963285</v>
+        <v>159.2755745963286</v>
       </c>
     </row>
     <row r="635">
@@ -7532,7 +7532,7 @@
         <v>473</v>
       </c>
       <c r="C646" t="n">
-        <v>464.63232216399</v>
+        <v>464.6323221639899</v>
       </c>
     </row>
     <row r="647">
@@ -7686,7 +7686,7 @@
         <v>156</v>
       </c>
       <c r="C660" t="n">
-        <v>159.4205467468534</v>
+        <v>159.4205467468535</v>
       </c>
     </row>
     <row r="661">
@@ -7752,7 +7752,7 @@
         <v>589</v>
       </c>
       <c r="C666" t="n">
-        <v>586.4552432593052</v>
+        <v>586.4552432593051</v>
       </c>
     </row>
     <row r="667">
@@ -7774,7 +7774,7 @@
         <v>530</v>
       </c>
       <c r="C668" t="n">
-        <v>546.5833248081676</v>
+        <v>546.5833248081677</v>
       </c>
     </row>
     <row r="669">
@@ -7807,7 +7807,7 @@
         <v>478</v>
       </c>
       <c r="C671" t="n">
-        <v>442.4040686275216</v>
+        <v>442.4040686275217</v>
       </c>
     </row>
     <row r="672">
@@ -7851,7 +7851,7 @@
         <v>568</v>
       </c>
       <c r="C675" t="n">
-        <v>550.3600720357074</v>
+        <v>550.3600720357075</v>
       </c>
     </row>
     <row r="676">
@@ -7884,7 +7884,7 @@
         <v>400</v>
       </c>
       <c r="C678" t="n">
-        <v>360.8710260591461</v>
+        <v>360.871026059146</v>
       </c>
     </row>
     <row r="679">
@@ -8016,7 +8016,7 @@
         <v>559</v>
       </c>
       <c r="C690" t="n">
-        <v>550.011858305208</v>
+        <v>550.0118583052081</v>
       </c>
     </row>
     <row r="691">
@@ -8027,7 +8027,7 @@
         <v>531</v>
       </c>
       <c r="C691" t="n">
-        <v>555.345550273526</v>
+        <v>555.3455502735259</v>
       </c>
     </row>
     <row r="692">
@@ -8247,7 +8247,7 @@
         <v>194</v>
       </c>
       <c r="C711" t="n">
-        <v>203.7585577922751</v>
+        <v>203.758557792275</v>
       </c>
     </row>
     <row r="712">
@@ -8269,7 +8269,7 @@
         <v>298</v>
       </c>
       <c r="C713" t="n">
-        <v>290.7873603919616</v>
+        <v>290.7873603919617</v>
       </c>
     </row>
     <row r="714">
@@ -8280,7 +8280,7 @@
         <v>388</v>
       </c>
       <c r="C714" t="n">
-        <v>369.4483885816847</v>
+        <v>369.4483885816848</v>
       </c>
     </row>
     <row r="715">
@@ -8313,7 +8313,7 @@
         <v>483</v>
       </c>
       <c r="C717" t="n">
-        <v>433.375113632842</v>
+        <v>433.3751136328421</v>
       </c>
     </row>
     <row r="718">
@@ -8379,7 +8379,7 @@
         <v>395</v>
       </c>
       <c r="C723" t="n">
-        <v>418.474268552408</v>
+        <v>418.4742685524081</v>
       </c>
     </row>
     <row r="724">
@@ -8401,7 +8401,7 @@
         <v>337</v>
       </c>
       <c r="C725" t="n">
-        <v>361.5700407855525</v>
+        <v>361.5700407855526</v>
       </c>
     </row>
     <row r="726">
@@ -8434,7 +8434,7 @@
         <v>216</v>
       </c>
       <c r="C728" t="n">
-        <v>179.7415668394854</v>
+        <v>179.7415668394855</v>
       </c>
     </row>
     <row r="729">
@@ -8467,7 +8467,7 @@
         <v>72</v>
       </c>
       <c r="C731" t="n">
-        <v>92.81894988110407</v>
+        <v>92.81894988110406</v>
       </c>
     </row>
     <row r="732">
@@ -8522,7 +8522,7 @@
         <v>634</v>
       </c>
       <c r="C736" t="n">
-        <v>589.5975005613817</v>
+        <v>589.5975005613816</v>
       </c>
     </row>
     <row r="737">
@@ -8544,7 +8544,7 @@
         <v>593</v>
       </c>
       <c r="C738" t="n">
-        <v>600.0562491662049</v>
+        <v>600.0562491662048</v>
       </c>
     </row>
     <row r="739">
@@ -8555,7 +8555,7 @@
         <v>591</v>
       </c>
       <c r="C739" t="n">
-        <v>625.0425687501775</v>
+        <v>625.0425687501776</v>
       </c>
     </row>
     <row r="740">
@@ -8654,7 +8654,7 @@
         <v>390</v>
       </c>
       <c r="C748" t="n">
-        <v>424.702505994604</v>
+        <v>424.7025059946041</v>
       </c>
     </row>
     <row r="749">
@@ -8720,7 +8720,7 @@
         <v>192</v>
       </c>
       <c r="C754" t="n">
-        <v>125.6133975646076</v>
+        <v>125.6133975646077</v>
       </c>
     </row>
     <row r="755">
@@ -8764,7 +8764,7 @@
         <v>392</v>
       </c>
       <c r="C758" t="n">
-        <v>504.0049451691237</v>
+        <v>504.0049451691236</v>
       </c>
     </row>
     <row r="759">
@@ -8786,7 +8786,7 @@
         <v>704</v>
       </c>
       <c r="C760" t="n">
-        <v>590.4847506558219</v>
+        <v>590.4847506558218</v>
       </c>
     </row>
     <row r="761">
@@ -8830,7 +8830,7 @@
         <v>557</v>
       </c>
       <c r="C764" t="n">
-        <v>563.1323387989603</v>
+        <v>563.1323387989604</v>
       </c>
     </row>
     <row r="765">
@@ -8852,7 +8852,7 @@
         <v>448</v>
       </c>
       <c r="C766" t="n">
-        <v>448.6615204407184</v>
+        <v>448.6615204407183</v>
       </c>
     </row>
     <row r="767">
@@ -8907,7 +8907,7 @@
         <v>454</v>
       </c>
       <c r="C771" t="n">
-        <v>505.4694446537236</v>
+        <v>505.4694446537235</v>
       </c>
     </row>
     <row r="772">
@@ -8918,7 +8918,7 @@
         <v>464</v>
       </c>
       <c r="C772" t="n">
-        <v>431.8658667334596</v>
+        <v>431.8658667334597</v>
       </c>
     </row>
     <row r="773">
@@ -9039,7 +9039,7 @@
         <v>464</v>
       </c>
       <c r="C783" t="n">
-        <v>465.1996889203042</v>
+        <v>465.1996889203043</v>
       </c>
     </row>
     <row r="784">
@@ -9061,7 +9061,7 @@
         <v>663</v>
       </c>
       <c r="C785" t="n">
-        <v>600.0170912111383</v>
+        <v>600.0170912111384</v>
       </c>
     </row>
     <row r="786">
@@ -9094,7 +9094,7 @@
         <v>544</v>
       </c>
       <c r="C788" t="n">
-        <v>561.8731502903703</v>
+        <v>561.8731502903702</v>
       </c>
     </row>
     <row r="789">
@@ -9127,7 +9127,7 @@
         <v>449</v>
       </c>
       <c r="C791" t="n">
-        <v>443.8932561320889</v>
+        <v>443.893256132089</v>
       </c>
     </row>
     <row r="792">
@@ -9193,7 +9193,7 @@
         <v>479</v>
       </c>
       <c r="C797" t="n">
-        <v>415.0919145151774</v>
+        <v>415.0919145151773</v>
       </c>
     </row>
     <row r="798">
@@ -9204,7 +9204,7 @@
         <v>365</v>
       </c>
       <c r="C798" t="n">
-        <v>418.6658318608244</v>
+        <v>418.6658318608243</v>
       </c>
     </row>
     <row r="799">
@@ -9336,7 +9336,7 @@
         <v>589</v>
       </c>
       <c r="C810" t="n">
-        <v>552.5234826902131</v>
+        <v>552.5234826902132</v>
       </c>
     </row>
     <row r="811">
@@ -9347,7 +9347,7 @@
         <v>596</v>
       </c>
       <c r="C811" t="n">
-        <v>560.8517738240888</v>
+        <v>560.8517738240887</v>
       </c>
     </row>
     <row r="812">
@@ -9435,7 +9435,7 @@
         <v>282</v>
       </c>
       <c r="C819" t="n">
-        <v>590.0714507640026</v>
+        <v>590.0714507640024</v>
       </c>
     </row>
     <row r="820">
@@ -9578,7 +9578,7 @@
         <v>175</v>
       </c>
       <c r="C832" t="n">
-        <v>211.5727961306294</v>
+        <v>211.5727961306295</v>
       </c>
     </row>
     <row r="833">
@@ -9644,7 +9644,7 @@
         <v>412</v>
       </c>
       <c r="C838" t="n">
-        <v>417.1313152227697</v>
+        <v>417.1313152227696</v>
       </c>
     </row>
     <row r="839">
@@ -9699,7 +9699,7 @@
         <v>372</v>
       </c>
       <c r="C843" t="n">
-        <v>445.1794446252309</v>
+        <v>445.1794446252308</v>
       </c>
     </row>
     <row r="844">
@@ -9754,7 +9754,7 @@
         <v>219</v>
       </c>
       <c r="C848" t="n">
-        <v>195.9715020831695</v>
+        <v>195.9715020831694</v>
       </c>
     </row>
     <row r="849">
@@ -9809,7 +9809,7 @@
         <v>137</v>
       </c>
       <c r="C853" t="n">
-        <v>364.3582170618794</v>
+        <v>364.3582170618795</v>
       </c>
     </row>
     <row r="854">
@@ -9820,7 +9820,7 @@
         <v>301</v>
       </c>
       <c r="C854" t="n">
-        <v>506.4558919285875</v>
+        <v>506.4558919285874</v>
       </c>
     </row>
     <row r="855">
@@ -9842,7 +9842,7 @@
         <v>627</v>
       </c>
       <c r="C856" t="n">
-        <v>571.3901628431855</v>
+        <v>571.3901628431854</v>
       </c>
     </row>
     <row r="857">
@@ -9864,7 +9864,7 @@
         <v>658</v>
       </c>
       <c r="C858" t="n">
-        <v>593.1439391718187</v>
+        <v>593.1439391718186</v>
       </c>
     </row>
     <row r="859">
@@ -9875,7 +9875,7 @@
         <v>595</v>
       </c>
       <c r="C859" t="n">
-        <v>580.7824805199311</v>
+        <v>580.782480519931</v>
       </c>
     </row>
     <row r="860">
@@ -9930,7 +9930,7 @@
         <v>451</v>
       </c>
       <c r="C864" t="n">
-        <v>460.1994115529431</v>
+        <v>460.1994115529432</v>
       </c>
     </row>
     <row r="865">
@@ -9952,7 +9952,7 @@
         <v>518</v>
       </c>
       <c r="C866" t="n">
-        <v>491.5933408293935</v>
+        <v>491.5933408293934</v>
       </c>
     </row>
     <row r="867">
@@ -10007,7 +10007,7 @@
         <v>352</v>
       </c>
       <c r="C871" t="n">
-        <v>349.6161812062362</v>
+        <v>349.6161812062363</v>
       </c>
     </row>
     <row r="872">
@@ -10062,7 +10062,7 @@
         <v>176</v>
       </c>
       <c r="C876" t="n">
-        <v>186.787911936493</v>
+        <v>186.7879119364929</v>
       </c>
     </row>
     <row r="877">
@@ -10073,7 +10073,7 @@
         <v>199</v>
       </c>
       <c r="C877" t="n">
-        <v>281.1986800034344</v>
+        <v>281.1986800034345</v>
       </c>
     </row>
     <row r="878">
@@ -10117,7 +10117,7 @@
         <v>575</v>
       </c>
       <c r="C881" t="n">
-        <v>570.8141939481592</v>
+        <v>570.8141939481593</v>
       </c>
     </row>
     <row r="882">
@@ -10128,7 +10128,7 @@
         <v>596</v>
       </c>
       <c r="C882" t="n">
-        <v>574.8994394991279</v>
+        <v>574.899439499128</v>
       </c>
     </row>
     <row r="883">
@@ -10183,7 +10183,7 @@
         <v>465</v>
       </c>
       <c r="C887" t="n">
-        <v>481.5258602518533</v>
+        <v>481.5258602518534</v>
       </c>
     </row>
     <row r="888">
@@ -10194,7 +10194,7 @@
         <v>542</v>
       </c>
       <c r="C888" t="n">
-        <v>474.7697800971671</v>
+        <v>474.7697800971673</v>
       </c>
     </row>
     <row r="889">
@@ -10249,7 +10249,7 @@
         <v>481</v>
       </c>
       <c r="C893" t="n">
-        <v>466.8396088765254</v>
+        <v>466.8396088765253</v>
       </c>
     </row>
     <row r="894">
@@ -10392,7 +10392,7 @@
         <v>91</v>
       </c>
       <c r="C906" t="n">
-        <v>184.7586604842809</v>
+        <v>184.758660484281</v>
       </c>
     </row>
     <row r="907">
@@ -10425,7 +10425,7 @@
         <v>113</v>
       </c>
       <c r="C909" t="n">
-        <v>375.1688446103975</v>
+        <v>375.1688446103976</v>
       </c>
     </row>
     <row r="910">
@@ -10546,7 +10546,7 @@
         <v>221</v>
       </c>
       <c r="C920" t="n">
-        <v>186.2472406855911</v>
+        <v>186.2472406855912</v>
       </c>
     </row>
     <row r="921">
@@ -10601,7 +10601,7 @@
         <v>122</v>
       </c>
       <c r="C925" t="n">
-        <v>355.2223180180457</v>
+        <v>355.2223180180455</v>
       </c>
     </row>
     <row r="926">
@@ -10667,7 +10667,7 @@
         <v>591</v>
       </c>
       <c r="C931" t="n">
-        <v>588.4610716777697</v>
+        <v>588.4610716777696</v>
       </c>
     </row>
     <row r="932">
@@ -10678,7 +10678,7 @@
         <v>527</v>
       </c>
       <c r="C932" t="n">
-        <v>544.22037686811</v>
+        <v>544.2203768681101</v>
       </c>
     </row>
     <row r="933">
@@ -10700,7 +10700,7 @@
         <v>451</v>
       </c>
       <c r="C934" t="n">
-        <v>454.8871369926088</v>
+        <v>454.8871369926087</v>
       </c>
     </row>
     <row r="935">
@@ -10810,7 +10810,7 @@
         <v>199</v>
       </c>
       <c r="C944" t="n">
-        <v>184.7046352453325</v>
+        <v>184.7046352453324</v>
       </c>
     </row>
     <row r="945">
@@ -10876,7 +10876,7 @@
         <v>326</v>
       </c>
       <c r="C950" t="n">
-        <v>327.1941751471149</v>
+        <v>327.1941751471148</v>
       </c>
     </row>
     <row r="951">
@@ -10964,7 +10964,7 @@
         <v>484</v>
       </c>
       <c r="C958" t="n">
-        <v>458.7218378337969</v>
+        <v>458.7218378337971</v>
       </c>
     </row>
     <row r="959">
@@ -10986,7 +10986,7 @@
         <v>472</v>
       </c>
       <c r="C960" t="n">
-        <v>469.2849612139349</v>
+        <v>469.284961213935</v>
       </c>
     </row>
     <row r="961">
@@ -11019,7 +11019,7 @@
         <v>541</v>
       </c>
       <c r="C963" t="n">
-        <v>530.1874032437488</v>
+        <v>530.1874032437487</v>
       </c>
     </row>
     <row r="964">
@@ -11140,7 +11140,7 @@
         <v>356</v>
       </c>
       <c r="C974" t="n">
-        <v>328.2972619271076</v>
+        <v>328.2972619271075</v>
       </c>
     </row>
     <row r="975">
@@ -11195,7 +11195,7 @@
         <v>643</v>
       </c>
       <c r="C979" t="n">
-        <v>583.2527437880256</v>
+        <v>583.2527437880254</v>
       </c>
     </row>
     <row r="980">
@@ -11250,7 +11250,7 @@
         <v>502</v>
       </c>
       <c r="C984" t="n">
-        <v>444.2640637990035</v>
+        <v>444.2640637990036</v>
       </c>
     </row>
     <row r="985">
@@ -11305,7 +11305,7 @@
         <v>374</v>
       </c>
       <c r="C989" t="n">
-        <v>441.958371213967</v>
+        <v>441.9583712139671</v>
       </c>
     </row>
     <row r="990">
@@ -11316,7 +11316,7 @@
         <v>369</v>
       </c>
       <c r="C990" t="n">
-        <v>366.2581636903518</v>
+        <v>366.2581636903519</v>
       </c>
     </row>
     <row r="991">
@@ -11426,7 +11426,7 @@
         <v>598</v>
       </c>
       <c r="C1000" t="n">
-        <v>523.9546117153182</v>
+        <v>523.954611715318</v>
       </c>
     </row>
     <row r="1001">
@@ -11459,7 +11459,7 @@
         <v>575</v>
       </c>
       <c r="C1003" t="n">
-        <v>557.061214628591</v>
+        <v>557.0612146285908</v>
       </c>
     </row>
     <row r="1004">
@@ -11525,7 +11525,7 @@
         <v>558</v>
       </c>
       <c r="C1009" t="n">
-        <v>515.8724738532625</v>
+        <v>515.8724738532626</v>
       </c>
     </row>
     <row r="1010">
@@ -11547,7 +11547,7 @@
         <v>604</v>
       </c>
       <c r="C1011" t="n">
-        <v>539.3398573602462</v>
+        <v>539.3398573602464</v>
       </c>
     </row>
     <row r="1012">
@@ -11602,7 +11602,7 @@
         <v>368</v>
       </c>
       <c r="C1016" t="n">
-        <v>360.2870823120101</v>
+        <v>360.2870823120102</v>
       </c>
     </row>
     <row r="1017">
@@ -11723,7 +11723,7 @@
         <v>381</v>
       </c>
       <c r="C1027" t="n">
-        <v>346.0355852885879</v>
+        <v>346.035585288588</v>
       </c>
     </row>
     <row r="1028">
@@ -11734,7 +11734,7 @@
         <v>138</v>
       </c>
       <c r="C1028" t="n">
-        <v>410.3703602718645</v>
+        <v>410.3703602718644</v>
       </c>
     </row>
     <row r="1029">
@@ -11943,7 +11943,7 @@
         <v>498</v>
       </c>
       <c r="C1047" t="n">
-        <v>474.8693142858194</v>
+        <v>474.8693142858193</v>
       </c>
     </row>
     <row r="1048">
@@ -11976,7 +11976,7 @@
         <v>622</v>
       </c>
       <c r="C1050" t="n">
-        <v>587.5746267286672</v>
+        <v>587.5746267286671</v>
       </c>
     </row>
     <row r="1051">
@@ -11987,7 +11987,7 @@
         <v>559</v>
       </c>
       <c r="C1051" t="n">
-        <v>575.8474692366686</v>
+        <v>575.8474692366685</v>
       </c>
     </row>
     <row r="1052">
@@ -12042,7 +12042,7 @@
         <v>471</v>
       </c>
       <c r="C1056" t="n">
-        <v>466.3156480646389</v>
+        <v>466.315648064639</v>
       </c>
     </row>
     <row r="1057">
@@ -12053,7 +12053,7 @@
         <v>457</v>
       </c>
       <c r="C1057" t="n">
-        <v>479.6127674057701</v>
+        <v>479.6127674057699</v>
       </c>
     </row>
     <row r="1058">
@@ -12086,7 +12086,7 @@
         <v>395</v>
       </c>
       <c r="C1060" t="n">
-        <v>415.82563300208</v>
+        <v>415.8256330020801</v>
       </c>
     </row>
     <row r="1061">
@@ -12141,7 +12141,7 @@
         <v>181</v>
       </c>
       <c r="C1065" t="n">
-        <v>164.0541892556044</v>
+        <v>164.0541892556045</v>
       </c>
     </row>
     <row r="1066">
@@ -12185,7 +12185,7 @@
         <v>155</v>
       </c>
       <c r="C1069" t="n">
-        <v>277.4412297663076</v>
+        <v>277.4412297663077</v>
       </c>
     </row>
     <row r="1070">
@@ -12196,7 +12196,7 @@
         <v>342</v>
       </c>
       <c r="C1070" t="n">
-        <v>317.4488899884389</v>
+        <v>317.448889988439</v>
       </c>
     </row>
     <row r="1071">
@@ -12207,7 +12207,7 @@
         <v>499</v>
       </c>
       <c r="C1071" t="n">
-        <v>519.0962136942507</v>
+        <v>519.0962136942505</v>
       </c>
     </row>
     <row r="1072">
@@ -12218,7 +12218,7 @@
         <v>694</v>
       </c>
       <c r="C1072" t="n">
-        <v>631.8031006916585</v>
+        <v>631.8031006916584</v>
       </c>
     </row>
     <row r="1073">
@@ -12251,7 +12251,7 @@
         <v>566</v>
       </c>
       <c r="C1075" t="n">
-        <v>586.9201534436301</v>
+        <v>586.9201534436299</v>
       </c>
     </row>
     <row r="1076">
@@ -12295,7 +12295,7 @@
         <v>460</v>
       </c>
       <c r="C1079" t="n">
-        <v>462.6768922641851</v>
+        <v>462.6768922641852</v>
       </c>
     </row>
     <row r="1080">
@@ -12482,7 +12482,7 @@
         <v>603</v>
       </c>
       <c r="C1096" t="n">
-        <v>567.8486821715359</v>
+        <v>567.8486821715358</v>
       </c>
     </row>
     <row r="1097">
@@ -12493,7 +12493,7 @@
         <v>685</v>
       </c>
       <c r="C1097" t="n">
-        <v>588.6088865368781</v>
+        <v>588.6088865368782</v>
       </c>
     </row>
     <row r="1098">
@@ -12504,7 +12504,7 @@
         <v>552</v>
       </c>
       <c r="C1098" t="n">
-        <v>602.8500899792532</v>
+        <v>602.8500899792533</v>
       </c>
     </row>
     <row r="1099">
@@ -12526,7 +12526,7 @@
         <v>363</v>
       </c>
       <c r="C1100" t="n">
-        <v>441.1070788223548</v>
+        <v>441.1070788223547</v>
       </c>
     </row>
     <row r="1101">
@@ -12581,7 +12581,7 @@
         <v>490</v>
       </c>
       <c r="C1105" t="n">
-        <v>509.7127717960748</v>
+        <v>509.7127717960747</v>
       </c>
     </row>
     <row r="1106">
@@ -12592,7 +12592,7 @@
         <v>446</v>
       </c>
       <c r="C1106" t="n">
-        <v>512.3816946265306</v>
+        <v>512.3816946265305</v>
       </c>
     </row>
     <row r="1107">
@@ -12614,7 +12614,7 @@
         <v>470</v>
       </c>
       <c r="C1108" t="n">
-        <v>484.5639706279338</v>
+        <v>484.5639706279339</v>
       </c>
     </row>
     <row r="1109">
@@ -12702,7 +12702,7 @@
         <v>210</v>
       </c>
       <c r="C1116" t="n">
-        <v>193.7721387056226</v>
+        <v>193.7721387056227</v>
       </c>
     </row>
     <row r="1117">
@@ -12790,7 +12790,7 @@
         <v>568</v>
       </c>
       <c r="C1124" t="n">
-        <v>550.7947295587261</v>
+        <v>550.7947295587262</v>
       </c>
     </row>
     <row r="1125">
@@ -12878,7 +12878,7 @@
         <v>588</v>
       </c>
       <c r="C1132" t="n">
-        <v>540.0644664612095</v>
+        <v>540.0644664612093</v>
       </c>
     </row>
     <row r="1133">
@@ -12933,7 +12933,7 @@
         <v>418</v>
       </c>
       <c r="C1137" t="n">
-        <v>356.4518586845999</v>
+        <v>356.4518586845998</v>
       </c>
     </row>
     <row r="1138">
@@ -12944,7 +12944,7 @@
         <v>357</v>
       </c>
       <c r="C1138" t="n">
-        <v>337.8057128073593</v>
+        <v>337.8057128073594</v>
       </c>
     </row>
     <row r="1139">
@@ -13032,7 +13032,7 @@
         <v>425</v>
       </c>
       <c r="C1146" t="n">
-        <v>406.4657403889511</v>
+        <v>406.465740388951</v>
       </c>
     </row>
     <row r="1147">
@@ -13065,7 +13065,7 @@
         <v>464</v>
       </c>
       <c r="C1149" t="n">
-        <v>470.2650903081405</v>
+        <v>470.2650903081407</v>
       </c>
     </row>
     <row r="1150">
@@ -13131,7 +13131,7 @@
         <v>416</v>
       </c>
       <c r="C1155" t="n">
-        <v>442.1989257656514</v>
+        <v>442.1989257656515</v>
       </c>
     </row>
     <row r="1156">
@@ -13175,7 +13175,7 @@
         <v>252</v>
       </c>
       <c r="C1159" t="n">
-        <v>261.2202613746625</v>
+        <v>261.2202613746626</v>
       </c>
     </row>
     <row r="1160">
@@ -13241,7 +13241,7 @@
         <v>128</v>
       </c>
       <c r="C1165" t="n">
-        <v>187.9216031744249</v>
+        <v>187.921603174425</v>
       </c>
     </row>
     <row r="1166">
@@ -13252,7 +13252,7 @@
         <v>348</v>
       </c>
       <c r="C1166" t="n">
-        <v>328.4486627974277</v>
+        <v>328.4486627974276</v>
       </c>
     </row>
     <row r="1167">
@@ -13285,7 +13285,7 @@
         <v>667</v>
       </c>
       <c r="C1169" t="n">
-        <v>603.6095428529873</v>
+        <v>603.6095428529871</v>
       </c>
     </row>
     <row r="1170">
@@ -13318,7 +13318,7 @@
         <v>520</v>
       </c>
       <c r="C1172" t="n">
-        <v>548.5056328397861</v>
+        <v>548.5056328397862</v>
       </c>
     </row>
     <row r="1173">
@@ -13329,7 +13329,7 @@
         <v>491</v>
       </c>
       <c r="C1173" t="n">
-        <v>516.9351914562733</v>
+        <v>516.9351914562734</v>
       </c>
     </row>
     <row r="1174">
@@ -13351,7 +13351,7 @@
         <v>472</v>
       </c>
       <c r="C1175" t="n">
-        <v>449.5740256283905</v>
+        <v>449.5740256283906</v>
       </c>
     </row>
     <row r="1176">
@@ -13362,7 +13362,7 @@
         <v>475</v>
       </c>
       <c r="C1176" t="n">
-        <v>479.3449269878778</v>
+        <v>479.3449269878777</v>
       </c>
     </row>
     <row r="1177">
@@ -13384,7 +13384,7 @@
         <v>571</v>
       </c>
       <c r="C1178" t="n">
-        <v>504.9516936763888</v>
+        <v>504.9516936763889</v>
       </c>
     </row>
     <row r="1179">
@@ -13417,7 +13417,7 @@
         <v>340</v>
       </c>
       <c r="C1181" t="n">
-        <v>348.5738813289362</v>
+        <v>348.5738813289364</v>
       </c>
     </row>
     <row r="1182">
@@ -13428,7 +13428,7 @@
         <v>374</v>
       </c>
       <c r="C1182" t="n">
-        <v>297.0271820233123</v>
+        <v>297.0271820233124</v>
       </c>
     </row>
     <row r="1183">
@@ -13494,7 +13494,7 @@
         <v>106</v>
       </c>
       <c r="C1188" t="n">
-        <v>131.6371033297672</v>
+        <v>131.6371033297673</v>
       </c>
     </row>
     <row r="1189">
@@ -13527,7 +13527,7 @@
         <v>483</v>
       </c>
       <c r="C1191" t="n">
-        <v>469.0603816799657</v>
+        <v>469.0603816799656</v>
       </c>
     </row>
     <row r="1192">
@@ -13549,7 +13549,7 @@
         <v>668</v>
       </c>
       <c r="C1193" t="n">
-        <v>610.9816725969919</v>
+        <v>610.981672596992</v>
       </c>
     </row>
     <row r="1194">
@@ -13582,7 +13582,7 @@
         <v>572</v>
       </c>
       <c r="C1196" t="n">
-        <v>559.3675230723948</v>
+        <v>559.3675230723946</v>
       </c>
     </row>
     <row r="1197">
@@ -13604,7 +13604,7 @@
         <v>482</v>
       </c>
       <c r="C1198" t="n">
-        <v>511.1164071861308</v>
+        <v>511.116407186131</v>
       </c>
     </row>
     <row r="1199">
@@ -13626,7 +13626,7 @@
         <v>495</v>
       </c>
       <c r="C1200" t="n">
-        <v>467.5037556482148</v>
+        <v>467.503755648215</v>
       </c>
     </row>
     <row r="1201">
@@ -13648,7 +13648,7 @@
         <v>470</v>
       </c>
       <c r="C1202" t="n">
-        <v>518.9525643371981</v>
+        <v>518.9525643371979</v>
       </c>
     </row>
     <row r="1203">
@@ -13659,7 +13659,7 @@
         <v>461</v>
       </c>
       <c r="C1203" t="n">
-        <v>486.7013855008596</v>
+        <v>486.7013855008595</v>
       </c>
     </row>
     <row r="1204">
@@ -13714,7 +13714,7 @@
         <v>327</v>
       </c>
       <c r="C1208" t="n">
-        <v>283.5775448665935</v>
+        <v>283.5775448665934</v>
       </c>
     </row>
     <row r="1209">
@@ -13747,7 +13747,7 @@
         <v>200</v>
       </c>
       <c r="C1211" t="n">
-        <v>177.1007466543634</v>
+        <v>177.1007466543633</v>
       </c>
     </row>
     <row r="1212">
@@ -13824,7 +13824,7 @@
         <v>425</v>
       </c>
       <c r="C1218" t="n">
-        <v>588.2821133442078</v>
+        <v>588.2821133442077</v>
       </c>
     </row>
     <row r="1219">
@@ -13846,7 +13846,7 @@
         <v>636</v>
       </c>
       <c r="C1220" t="n">
-        <v>561.1136305331911</v>
+        <v>561.1136305331912</v>
       </c>
     </row>
     <row r="1221">
@@ -13857,7 +13857,7 @@
         <v>494</v>
       </c>
       <c r="C1221" t="n">
-        <v>554.5199745766735</v>
+        <v>554.5199745766736</v>
       </c>
     </row>
     <row r="1222">
@@ -13868,7 +13868,7 @@
         <v>500</v>
       </c>
       <c r="C1222" t="n">
-        <v>492.1306027205673</v>
+        <v>492.1306027205674</v>
       </c>
     </row>
     <row r="1223">
@@ -13879,7 +13879,7 @@
         <v>488</v>
       </c>
       <c r="C1223" t="n">
-        <v>505.1264647457301</v>
+        <v>505.1264647457302</v>
       </c>
     </row>
     <row r="1224">
@@ -13901,7 +13901,7 @@
         <v>593</v>
       </c>
       <c r="C1225" t="n">
-        <v>518.2086873429062</v>
+        <v>518.208687342906</v>
       </c>
     </row>
     <row r="1226">
@@ -14077,7 +14077,7 @@
         <v>623</v>
       </c>
       <c r="C1241" t="n">
-        <v>570.7695145782135</v>
+        <v>570.7695145782136</v>
       </c>
     </row>
     <row r="1242">
@@ -14088,7 +14088,7 @@
         <v>594</v>
       </c>
       <c r="C1242" t="n">
-        <v>567.9081311983172</v>
+        <v>567.9081311983171</v>
       </c>
     </row>
     <row r="1243">
@@ -14110,7 +14110,7 @@
         <v>592</v>
       </c>
       <c r="C1244" t="n">
-        <v>552.3773291102166</v>
+        <v>552.3773291102167</v>
       </c>
     </row>
     <row r="1245">
@@ -14187,7 +14187,7 @@
         <v>615</v>
       </c>
       <c r="C1251" t="n">
-        <v>580.4022186865977</v>
+        <v>580.4022186865978</v>
       </c>
     </row>
     <row r="1252">
@@ -14209,7 +14209,7 @@
         <v>491</v>
       </c>
       <c r="C1253" t="n">
-        <v>484.449639236938</v>
+        <v>484.4496392369381</v>
       </c>
     </row>
     <row r="1254">
@@ -14242,7 +14242,7 @@
         <v>407</v>
       </c>
       <c r="C1256" t="n">
-        <v>392.6833030463589</v>
+        <v>392.683303046359</v>
       </c>
     </row>
     <row r="1257">
@@ -14396,7 +14396,7 @@
         <v>463</v>
       </c>
       <c r="C1270" t="n">
-        <v>423.2613810923009</v>
+        <v>423.261381092301</v>
       </c>
     </row>
     <row r="1271">
@@ -14407,7 +14407,7 @@
         <v>454</v>
       </c>
       <c r="C1271" t="n">
-        <v>435.3179232123207</v>
+        <v>435.3179232123208</v>
       </c>
     </row>
     <row r="1272">
@@ -14451,7 +14451,7 @@
         <v>454</v>
       </c>
       <c r="C1275" t="n">
-        <v>428.7866393166434</v>
+        <v>428.7866393166435</v>
       </c>
     </row>
     <row r="1276">
@@ -14473,7 +14473,7 @@
         <v>369</v>
       </c>
       <c r="C1277" t="n">
-        <v>334.240258347125</v>
+        <v>334.2402583471251</v>
       </c>
     </row>
     <row r="1278">
@@ -14495,7 +14495,7 @@
         <v>227</v>
       </c>
       <c r="C1279" t="n">
-        <v>228.8244983369914</v>
+        <v>228.8244983369915</v>
       </c>
     </row>
     <row r="1280">
@@ -14572,7 +14572,7 @@
         <v>280</v>
       </c>
       <c r="C1286" t="n">
-        <v>330.9542862630963</v>
+        <v>330.9542862630962</v>
       </c>
     </row>
     <row r="1287">
@@ -14638,7 +14638,7 @@
         <v>564</v>
       </c>
       <c r="C1292" t="n">
-        <v>553.5316864511368</v>
+        <v>553.5316864511369</v>
       </c>
     </row>
     <row r="1293">
@@ -14693,7 +14693,7 @@
         <v>496</v>
       </c>
       <c r="C1297" t="n">
-        <v>515.6749875590444</v>
+        <v>515.6749875590446</v>
       </c>
     </row>
     <row r="1298">
@@ -14704,7 +14704,7 @@
         <v>562</v>
       </c>
       <c r="C1298" t="n">
-        <v>506.4429063981323</v>
+        <v>506.4429063981324</v>
       </c>
     </row>
     <row r="1299">
@@ -14715,7 +14715,7 @@
         <v>443</v>
       </c>
       <c r="C1299" t="n">
-        <v>464.5942046835208</v>
+        <v>464.5942046835207</v>
       </c>
     </row>
     <row r="1300">
@@ -14924,7 +14924,7 @@
         <v>473</v>
       </c>
       <c r="C1318" t="n">
-        <v>448.4764747222255</v>
+        <v>448.4764747222254</v>
       </c>
     </row>
     <row r="1319">
@@ -15067,7 +15067,7 @@
         <v>191</v>
       </c>
       <c r="C1331" t="n">
-        <v>182.9373047490353</v>
+        <v>182.9373047490354</v>
       </c>
     </row>
     <row r="1332">
@@ -15232,7 +15232,7 @@
         <v>514</v>
       </c>
       <c r="C1346" t="n">
-        <v>504.240538436745</v>
+        <v>504.2405384367449</v>
       </c>
     </row>
     <row r="1347">
@@ -15364,7 +15364,7 @@
         <v>177</v>
       </c>
       <c r="C1358" t="n">
-        <v>165.2889104186187</v>
+        <v>165.2889104186188</v>
       </c>
     </row>
     <row r="1359">
@@ -15430,7 +15430,7 @@
         <v>464</v>
       </c>
       <c r="C1364" t="n">
-        <v>431.7767031779086</v>
+        <v>431.7767031779085</v>
       </c>
     </row>
     <row r="1365">
@@ -15452,7 +15452,7 @@
         <v>427</v>
       </c>
       <c r="C1366" t="n">
-        <v>422.6386251865108</v>
+        <v>422.6386251865107</v>
       </c>
     </row>
     <row r="1367">
@@ -15639,7 +15639,7 @@
         <v>524</v>
       </c>
       <c r="C1383" t="n">
-        <v>521.0864560320767</v>
+        <v>521.0864560320766</v>
       </c>
     </row>
     <row r="1384">
@@ -15683,7 +15683,7 @@
         <v>588</v>
       </c>
       <c r="C1387" t="n">
-        <v>570.8334447801982</v>
+        <v>570.8334447801981</v>
       </c>
     </row>
     <row r="1388">
@@ -15694,7 +15694,7 @@
         <v>566</v>
       </c>
       <c r="C1388" t="n">
-        <v>553.4236005137652</v>
+        <v>553.4236005137653</v>
       </c>
     </row>
     <row r="1389">
@@ -15727,7 +15727,7 @@
         <v>482</v>
       </c>
       <c r="C1391" t="n">
-        <v>442.8100276765676</v>
+        <v>442.8100276765675</v>
       </c>
     </row>
     <row r="1392">
@@ -15760,7 +15760,7 @@
         <v>536</v>
       </c>
       <c r="C1394" t="n">
-        <v>470.3262614449356</v>
+        <v>470.3262614449357</v>
       </c>
     </row>
     <row r="1395">
@@ -15793,7 +15793,7 @@
         <v>341</v>
       </c>
       <c r="C1397" t="n">
-        <v>339.6503575411537</v>
+        <v>339.6503575411538</v>
       </c>
     </row>
     <row r="1398">
@@ -15848,7 +15848,7 @@
         <v>147</v>
       </c>
       <c r="C1402" t="n">
-        <v>150.9366905143334</v>
+        <v>150.9366905143333</v>
       </c>
     </row>
     <row r="1403">
@@ -15870,7 +15870,7 @@
         <v>115</v>
       </c>
       <c r="C1404" t="n">
-        <v>122.9468068483294</v>
+        <v>122.9468068483293</v>
       </c>
     </row>
     <row r="1405">
@@ -15958,7 +15958,7 @@
         <v>592</v>
       </c>
       <c r="C1412" t="n">
-        <v>558.7024960198173</v>
+        <v>558.7024960198172</v>
       </c>
     </row>
     <row r="1413">
@@ -16013,7 +16013,7 @@
         <v>435</v>
       </c>
       <c r="C1417" t="n">
-        <v>490.3829476100741</v>
+        <v>490.382947610074</v>
       </c>
     </row>
     <row r="1418">
@@ -16024,7 +16024,7 @@
         <v>475</v>
       </c>
       <c r="C1418" t="n">
-        <v>458.8587568347285</v>
+        <v>458.8587568347284</v>
       </c>
     </row>
     <row r="1419">
@@ -16112,7 +16112,7 @@
         <v>242</v>
       </c>
       <c r="C1426" t="n">
-        <v>194.3881090378556</v>
+        <v>194.3881090378555</v>
       </c>
     </row>
     <row r="1427">
@@ -16211,7 +16211,7 @@
         <v>637</v>
       </c>
       <c r="C1435" t="n">
-        <v>582.2651679563772</v>
+        <v>582.2651679563771</v>
       </c>
     </row>
     <row r="1436">
@@ -16255,7 +16255,7 @@
         <v>410</v>
       </c>
       <c r="C1439" t="n">
-        <v>467.8030587218445</v>
+        <v>467.8030587218446</v>
       </c>
     </row>
     <row r="1440">
@@ -16299,7 +16299,7 @@
         <v>567</v>
       </c>
       <c r="C1443" t="n">
-        <v>541.1414087099317</v>
+        <v>541.1414087099316</v>
       </c>
     </row>
     <row r="1444">
@@ -16321,7 +16321,7 @@
         <v>426</v>
       </c>
       <c r="C1445" t="n">
-        <v>412.0915330147951</v>
+        <v>412.0915330147952</v>
       </c>
     </row>
     <row r="1446">
@@ -16376,7 +16376,7 @@
         <v>265</v>
       </c>
       <c r="C1450" t="n">
-        <v>234.432919911905</v>
+        <v>234.4329199119051</v>
       </c>
     </row>
     <row r="1451">
@@ -16398,7 +16398,7 @@
         <v>167</v>
       </c>
       <c r="C1452" t="n">
-        <v>208.0659364170129</v>
+        <v>208.0659364170128</v>
       </c>
     </row>
     <row r="1453">
@@ -16464,7 +16464,7 @@
         <v>571</v>
       </c>
       <c r="C1458" t="n">
-        <v>571.8002590664056</v>
+        <v>571.8002590664055</v>
       </c>
     </row>
     <row r="1459">
@@ -16475,7 +16475,7 @@
         <v>645</v>
       </c>
       <c r="C1459" t="n">
-        <v>553.9810353504693</v>
+        <v>553.9810353504694</v>
       </c>
     </row>
     <row r="1460">
@@ -16486,7 +16486,7 @@
         <v>554</v>
       </c>
       <c r="C1460" t="n">
-        <v>550.0058748037658</v>
+        <v>550.0058748037659</v>
       </c>
     </row>
     <row r="1461">
@@ -16508,7 +16508,7 @@
         <v>473</v>
       </c>
       <c r="C1462" t="n">
-        <v>483.1665712777983</v>
+        <v>483.1665712777984</v>
       </c>
     </row>
     <row r="1463">
@@ -16519,7 +16519,7 @@
         <v>500</v>
       </c>
       <c r="C1463" t="n">
-        <v>488.0616042606174</v>
+        <v>488.0616042606173</v>
       </c>
     </row>
     <row r="1464">
@@ -16563,7 +16563,7 @@
         <v>656</v>
       </c>
       <c r="C1467" t="n">
-        <v>544.9714791271045</v>
+        <v>544.9714791271047</v>
       </c>
     </row>
     <row r="1468">
@@ -16585,7 +16585,7 @@
         <v>473</v>
       </c>
       <c r="C1469" t="n">
-        <v>470.7430699910034</v>
+        <v>470.7430699910033</v>
       </c>
     </row>
     <row r="1470">
@@ -16629,7 +16629,7 @@
         <v>386</v>
       </c>
       <c r="C1473" t="n">
-        <v>339.6833257519874</v>
+        <v>339.6833257519875</v>
       </c>
     </row>
     <row r="1474">
@@ -16695,7 +16695,7 @@
         <v>138</v>
       </c>
       <c r="C1479" t="n">
-        <v>171.7355073399151</v>
+        <v>171.7355073399152</v>
       </c>
     </row>
     <row r="1480">
@@ -16739,7 +16739,7 @@
         <v>484</v>
       </c>
       <c r="C1483" t="n">
-        <v>420.2313590201629</v>
+        <v>420.2313590201628</v>
       </c>
     </row>
     <row r="1484">
@@ -16772,7 +16772,7 @@
         <v>443</v>
       </c>
       <c r="C1486" t="n">
-        <v>449.9230603286723</v>
+        <v>449.9230603286724</v>
       </c>
     </row>
     <row r="1487">
@@ -16805,7 +16805,7 @@
         <v>483</v>
       </c>
       <c r="C1489" t="n">
-        <v>462.9131634002249</v>
+        <v>462.913163400225</v>
       </c>
     </row>
     <row r="1490">
@@ -16816,7 +16816,7 @@
         <v>494</v>
       </c>
       <c r="C1490" t="n">
-        <v>457.689473498628</v>
+        <v>457.6894734986282</v>
       </c>
     </row>
     <row r="1491">
@@ -16838,7 +16838,7 @@
         <v>366</v>
       </c>
       <c r="C1492" t="n">
-        <v>407.1664936665098</v>
+        <v>407.16649366651</v>
       </c>
     </row>
     <row r="1493">
@@ -17003,7 +17003,7 @@
         <v>645</v>
       </c>
       <c r="C1507" t="n">
-        <v>553.6611448329058</v>
+        <v>553.661144832906</v>
       </c>
     </row>
     <row r="1508">
@@ -17014,7 +17014,7 @@
         <v>554</v>
       </c>
       <c r="C1508" t="n">
-        <v>549.7692830677991</v>
+        <v>549.7692830677992</v>
       </c>
     </row>
     <row r="1509">
@@ -17058,7 +17058,7 @@
         <v>562</v>
       </c>
       <c r="C1512" t="n">
-        <v>510.5278372488464</v>
+        <v>510.5278372488463</v>
       </c>
     </row>
     <row r="1513">
@@ -17091,7 +17091,7 @@
         <v>656</v>
       </c>
       <c r="C1515" t="n">
-        <v>544.7348873911378</v>
+        <v>544.7348873911379</v>
       </c>
     </row>
     <row r="1516">
@@ -17124,7 +17124,7 @@
         <v>433</v>
       </c>
       <c r="C1518" t="n">
-        <v>412.4957905497757</v>
+        <v>412.4957905497758</v>
       </c>
     </row>
     <row r="1519">
@@ -17256,7 +17256,7 @@
         <v>574</v>
       </c>
       <c r="C1530" t="n">
-        <v>604.2609656687478</v>
+        <v>604.2609656687476</v>
       </c>
     </row>
     <row r="1531">
@@ -17267,7 +17267,7 @@
         <v>570</v>
       </c>
       <c r="C1531" t="n">
-        <v>581.872552948859</v>
+        <v>581.8725529488592</v>
       </c>
     </row>
     <row r="1532">
@@ -17289,7 +17289,7 @@
         <v>463</v>
       </c>
       <c r="C1533" t="n">
-        <v>495.9847551444793</v>
+        <v>495.9847551444792</v>
       </c>
     </row>
     <row r="1534">
@@ -17300,7 +17300,7 @@
         <v>421</v>
       </c>
       <c r="C1534" t="n">
-        <v>462.7440830154193</v>
+        <v>462.7440830154194</v>
       </c>
     </row>
     <row r="1535">
@@ -17333,7 +17333,7 @@
         <v>449</v>
       </c>
       <c r="C1537" t="n">
-        <v>488.4845973442651</v>
+        <v>488.484597344265</v>
       </c>
     </row>
     <row r="1538">
@@ -17377,7 +17377,7 @@
         <v>350</v>
       </c>
       <c r="C1541" t="n">
-        <v>353.3428084027361</v>
+        <v>353.342808402736</v>
       </c>
     </row>
     <row r="1542">
@@ -17432,7 +17432,7 @@
         <v>277</v>
       </c>
       <c r="C1546" t="n">
-        <v>191.9886081635625</v>
+        <v>191.9886081635626</v>
       </c>
     </row>
     <row r="1547">
@@ -17443,7 +17443,7 @@
         <v>192</v>
       </c>
       <c r="C1547" t="n">
-        <v>190.8308359728739</v>
+        <v>190.8308359728738</v>
       </c>
     </row>
     <row r="1548">
@@ -17542,7 +17542,7 @@
         <v>530</v>
       </c>
       <c r="C1556" t="n">
-        <v>569.5240328354656</v>
+        <v>569.5240328354655</v>
       </c>
     </row>
     <row r="1557">
@@ -17586,7 +17586,7 @@
         <v>458</v>
       </c>
       <c r="C1560" t="n">
-        <v>487.7239137638969</v>
+        <v>487.7239137638968</v>
       </c>
     </row>
     <row r="1561">
@@ -17597,7 +17597,7 @@
         <v>502</v>
       </c>
       <c r="C1561" t="n">
-        <v>488.8276064513792</v>
+        <v>488.8276064513791</v>
       </c>
     </row>
     <row r="1562">
@@ -17773,7 +17773,7 @@
         <v>514</v>
       </c>
       <c r="C1577" t="n">
-        <v>572.6241398647838</v>
+        <v>572.624139864784</v>
       </c>
     </row>
     <row r="1578">
@@ -17784,7 +17784,7 @@
         <v>538</v>
       </c>
       <c r="C1578" t="n">
-        <v>542.3655697596078</v>
+        <v>542.3655697596079</v>
       </c>
     </row>
     <row r="1579">
@@ -17905,7 +17905,7 @@
         <v>458</v>
       </c>
       <c r="C1589" t="n">
-        <v>486.0981682575096</v>
+        <v>486.0981682575097</v>
       </c>
     </row>
     <row r="1590">
@@ -17927,7 +17927,7 @@
         <v>348</v>
       </c>
       <c r="C1591" t="n">
-        <v>405.7009818939263</v>
+        <v>405.7009818939264</v>
       </c>
     </row>
     <row r="1592">
@@ -17949,7 +17949,7 @@
         <v>381</v>
       </c>
       <c r="C1593" t="n">
-        <v>358.2102039708419</v>
+        <v>358.210203970842</v>
       </c>
     </row>
     <row r="1594">
@@ -17993,7 +17993,7 @@
         <v>276</v>
       </c>
       <c r="C1597" t="n">
-        <v>269.2344709131278</v>
+        <v>269.2344709131277</v>
       </c>
     </row>
     <row r="1598">
@@ -18026,7 +18026,7 @@
         <v>32</v>
       </c>
       <c r="C1600" t="n">
-        <v>167.9846468141577</v>
+        <v>167.9846468141578</v>
       </c>
     </row>
     <row r="1601">
@@ -18125,7 +18125,7 @@
         <v>471</v>
       </c>
       <c r="C1609" t="n">
-        <v>486.6262026164973</v>
+        <v>486.6262026164974</v>
       </c>
     </row>
     <row r="1610">
@@ -18136,7 +18136,7 @@
         <v>446</v>
       </c>
       <c r="C1610" t="n">
-        <v>444.6676120803618</v>
+        <v>444.6676120803619</v>
       </c>
     </row>
     <row r="1611">
@@ -18169,7 +18169,7 @@
         <v>385</v>
       </c>
       <c r="C1613" t="n">
-        <v>356.9751579309406</v>
+        <v>356.9751579309405</v>
       </c>
     </row>
     <row r="1614">
@@ -18235,7 +18235,7 @@
         <v>88</v>
       </c>
       <c r="C1619" t="n">
-        <v>91.59149121652659</v>
+        <v>91.59149121652658</v>
       </c>
     </row>
     <row r="1620">
@@ -18268,7 +18268,7 @@
         <v>326</v>
       </c>
       <c r="C1622" t="n">
-        <v>322.5170820770337</v>
+        <v>322.5170820770338</v>
       </c>
     </row>
     <row r="1623">
@@ -18400,7 +18400,7 @@
         <v>497</v>
       </c>
       <c r="C1634" t="n">
-        <v>457.6560435918625</v>
+        <v>457.6560435918624</v>
       </c>
     </row>
     <row r="1635">
@@ -18521,7 +18521,7 @@
         <v>133</v>
       </c>
       <c r="C1645" t="n">
-        <v>316.0376155582704</v>
+        <v>316.0376155582703</v>
       </c>
     </row>
     <row r="1646">
@@ -18554,7 +18554,7 @@
         <v>665</v>
       </c>
       <c r="C1648" t="n">
-        <v>604.4373903599751</v>
+        <v>604.437390359975</v>
       </c>
     </row>
     <row r="1649">
@@ -18576,7 +18576,7 @@
         <v>646</v>
       </c>
       <c r="C1650" t="n">
-        <v>607.2371781384654</v>
+        <v>607.2371781384655</v>
       </c>
     </row>
     <row r="1651">
@@ -18598,7 +18598,7 @@
         <v>555</v>
       </c>
       <c r="C1652" t="n">
-        <v>582.5672006348674</v>
+        <v>582.5672006348675</v>
       </c>
     </row>
     <row r="1653">
@@ -18620,7 +18620,7 @@
         <v>433</v>
       </c>
       <c r="C1654" t="n">
-        <v>453.3863129091296</v>
+        <v>453.3863129091297</v>
       </c>
     </row>
     <row r="1655">
@@ -18873,7 +18873,7 @@
         <v>546</v>
       </c>
       <c r="C1677" t="n">
-        <v>517.2644991682013</v>
+        <v>517.2644991682014</v>
       </c>
     </row>
     <row r="1678">
@@ -18972,7 +18972,7 @@
         <v>430</v>
       </c>
       <c r="C1686" t="n">
-        <v>375.4818952951302</v>
+        <v>375.4818952951301</v>
       </c>
     </row>
     <row r="1687">
@@ -19082,7 +19082,7 @@
         <v>588</v>
       </c>
       <c r="C1696" t="n">
-        <v>574.5929671162011</v>
+        <v>574.592967116201</v>
       </c>
     </row>
     <row r="1697">
@@ -19093,7 +19093,7 @@
         <v>576</v>
       </c>
       <c r="C1697" t="n">
-        <v>582.6127363310508</v>
+        <v>582.6127363310509</v>
       </c>
     </row>
     <row r="1698">
@@ -19170,7 +19170,7 @@
         <v>527</v>
       </c>
       <c r="C1704" t="n">
-        <v>449.4746752560945</v>
+        <v>449.4746752560947</v>
       </c>
     </row>
     <row r="1705">
@@ -19236,7 +19236,7 @@
         <v>404</v>
       </c>
       <c r="C1710" t="n">
-        <v>395.755866841038</v>
+        <v>395.7558668410381</v>
       </c>
     </row>
     <row r="1711">
@@ -19258,7 +19258,7 @@
         <v>438</v>
       </c>
       <c r="C1712" t="n">
-        <v>399.3516178542264</v>
+        <v>399.3516178542265</v>
       </c>
     </row>
     <row r="1713">
@@ -19357,7 +19357,7 @@
         <v>179</v>
       </c>
       <c r="C1721" t="n">
-        <v>150.308973765273</v>
+        <v>150.3089737652731</v>
       </c>
     </row>
     <row r="1722">
@@ -19412,7 +19412,7 @@
         <v>421</v>
       </c>
       <c r="C1726" t="n">
-        <v>391.5511816717603</v>
+        <v>391.5511816717604</v>
       </c>
     </row>
     <row r="1727">
@@ -19445,7 +19445,7 @@
         <v>438</v>
       </c>
       <c r="C1729" t="n">
-        <v>460.0291434971151</v>
+        <v>460.0291434971152</v>
       </c>
     </row>
     <row r="1730">
@@ -19478,7 +19478,7 @@
         <v>415</v>
       </c>
       <c r="C1732" t="n">
-        <v>396.5821760832526</v>
+        <v>396.5821760832527</v>
       </c>
     </row>
     <row r="1733">
@@ -19489,7 +19489,7 @@
         <v>356</v>
       </c>
       <c r="C1733" t="n">
-        <v>333.5655919378184</v>
+        <v>333.5655919378185</v>
       </c>
     </row>
     <row r="1734">
@@ -19555,7 +19555,7 @@
         <v>81</v>
       </c>
       <c r="C1739" t="n">
-        <v>90.65067852360343</v>
+        <v>90.65067852360346</v>
       </c>
     </row>
     <row r="1740">
@@ -19566,7 +19566,7 @@
         <v>92</v>
       </c>
       <c r="C1740" t="n">
-        <v>87.79396005520184</v>
+        <v>87.79396005520182</v>
       </c>
     </row>
     <row r="1741">
@@ -19643,7 +19643,7 @@
         <v>493</v>
       </c>
       <c r="C1747" t="n">
-        <v>570.0503844010074</v>
+        <v>570.0503844010076</v>
       </c>
     </row>
     <row r="1748">
@@ -19654,7 +19654,7 @@
         <v>494</v>
       </c>
       <c r="C1748" t="n">
-        <v>501.5124786143714</v>
+        <v>501.5124786143713</v>
       </c>
     </row>
     <row r="1749">
@@ -19709,7 +19709,7 @@
         <v>364</v>
       </c>
       <c r="C1753" t="n">
-        <v>461.1077794554911</v>
+        <v>461.107779455491</v>
       </c>
     </row>
     <row r="1754">
@@ -19753,7 +19753,7 @@
         <v>353</v>
       </c>
       <c r="C1757" t="n">
-        <v>205.4089273958494</v>
+        <v>205.4089273958495</v>
       </c>
     </row>
     <row r="1758">
@@ -19775,7 +19775,7 @@
         <v>292</v>
       </c>
       <c r="C1759" t="n">
-        <v>257.4465718521769</v>
+        <v>257.446571852177</v>
       </c>
     </row>
     <row r="1760">
@@ -19786,7 +19786,7 @@
         <v>263</v>
       </c>
       <c r="C1760" t="n">
-        <v>228.1596966617355</v>
+        <v>228.1596966617356</v>
       </c>
     </row>
     <row r="1761">
@@ -19841,7 +19841,7 @@
         <v>144</v>
       </c>
       <c r="C1765" t="n">
-        <v>197.9242631532512</v>
+        <v>197.9242631532513</v>
       </c>
     </row>
     <row r="1766">
@@ -19852,7 +19852,7 @@
         <v>370</v>
       </c>
       <c r="C1766" t="n">
-        <v>327.9230431687387</v>
+        <v>327.9230431687386</v>
       </c>
     </row>
     <row r="1767">
@@ -19874,7 +19874,7 @@
         <v>687</v>
       </c>
       <c r="C1768" t="n">
-        <v>588.4820839111569</v>
+        <v>588.4820839111568</v>
       </c>
     </row>
     <row r="1769">
@@ -19885,7 +19885,7 @@
         <v>665</v>
       </c>
       <c r="C1769" t="n">
-        <v>617.8892519105206</v>
+        <v>617.8892519105207</v>
       </c>
     </row>
     <row r="1770">
@@ -19995,7 +19995,7 @@
         <v>533</v>
       </c>
       <c r="C1779" t="n">
-        <v>505.0122356722637</v>
+        <v>505.0122356722638</v>
       </c>
     </row>
     <row r="1780">
@@ -20083,7 +20083,7 @@
         <v>212</v>
       </c>
       <c r="C1787" t="n">
-        <v>185.794673737519</v>
+        <v>185.7946737375189</v>
       </c>
     </row>
     <row r="1788">
@@ -20127,7 +20127,7 @@
         <v>436</v>
       </c>
       <c r="C1791" t="n">
-        <v>517.9232462235826</v>
+        <v>517.9232462235825</v>
       </c>
     </row>
     <row r="1792">
@@ -20171,7 +20171,7 @@
         <v>597</v>
       </c>
       <c r="C1795" t="n">
-        <v>574.3201768979309</v>
+        <v>574.320176897931</v>
       </c>
     </row>
     <row r="1796">
@@ -20182,7 +20182,7 @@
         <v>614</v>
       </c>
       <c r="C1796" t="n">
-        <v>586.7054639927035</v>
+        <v>586.7054639927034</v>
       </c>
     </row>
     <row r="1797">
@@ -20226,7 +20226,7 @@
         <v>522</v>
       </c>
       <c r="C1800" t="n">
-        <v>520.5971528685067</v>
+        <v>520.5971528685068</v>
       </c>
     </row>
     <row r="1801">
@@ -20281,7 +20281,7 @@
         <v>422</v>
       </c>
       <c r="C1805" t="n">
-        <v>417.5848622539166</v>
+        <v>417.5848622539168</v>
       </c>
     </row>
     <row r="1806">
@@ -20325,7 +20325,7 @@
         <v>254</v>
       </c>
       <c r="C1809" t="n">
-        <v>287.5583943788596</v>
+        <v>287.5583943788595</v>
       </c>
     </row>
     <row r="1810">
@@ -20512,7 +20512,7 @@
         <v>650</v>
       </c>
       <c r="C1826" t="n">
-        <v>550.304130489165</v>
+        <v>550.3041304891652</v>
       </c>
     </row>
     <row r="1827">
@@ -20765,7 +20765,7 @@
         <v>447</v>
       </c>
       <c r="C1849" t="n">
-        <v>457.2016395751799</v>
+        <v>457.20163957518</v>
       </c>
     </row>
     <row r="1850">
@@ -20809,7 +20809,7 @@
         <v>402</v>
       </c>
       <c r="C1853" t="n">
-        <v>347.4677012013714</v>
+        <v>347.4677012013715</v>
       </c>
     </row>
     <row r="1854">
@@ -20908,7 +20908,7 @@
         <v>317</v>
       </c>
       <c r="C1862" t="n">
-        <v>348.896603608704</v>
+        <v>348.8966036087041</v>
       </c>
     </row>
     <row r="1863">
@@ -20952,7 +20952,7 @@
         <v>594</v>
       </c>
       <c r="C1866" t="n">
-        <v>597.2395317885062</v>
+        <v>597.2395317885063</v>
       </c>
     </row>
     <row r="1867">
@@ -20985,7 +20985,7 @@
         <v>440</v>
       </c>
       <c r="C1869" t="n">
-        <v>532.0801917527093</v>
+        <v>532.0801917527092</v>
       </c>
     </row>
     <row r="1870">
@@ -21040,7 +21040,7 @@
         <v>562</v>
       </c>
       <c r="C1874" t="n">
-        <v>519.1334565330836</v>
+        <v>519.1334565330835</v>
       </c>
     </row>
     <row r="1875">
@@ -21117,7 +21117,7 @@
         <v>185</v>
       </c>
       <c r="C1881" t="n">
-        <v>153.7131273558148</v>
+        <v>153.7131273558147</v>
       </c>
     </row>
     <row r="1882">
@@ -21139,7 +21139,7 @@
         <v>100</v>
       </c>
       <c r="C1883" t="n">
-        <v>133.9069146056292</v>
+        <v>133.9069146056291</v>
       </c>
     </row>
     <row r="1884">
@@ -21161,7 +21161,7 @@
         <v>126</v>
       </c>
       <c r="C1885" t="n">
-        <v>310.6677744552686</v>
+        <v>310.6677744552685</v>
       </c>
     </row>
     <row r="1886">
@@ -21172,7 +21172,7 @@
         <v>317</v>
       </c>
       <c r="C1886" t="n">
-        <v>358.1254397899298</v>
+        <v>358.1254397899297</v>
       </c>
     </row>
     <row r="1887">
@@ -21238,7 +21238,7 @@
         <v>550</v>
       </c>
       <c r="C1892" t="n">
-        <v>558.921600432311</v>
+        <v>558.9216004323109</v>
       </c>
     </row>
     <row r="1893">
@@ -21249,7 +21249,7 @@
         <v>521</v>
       </c>
       <c r="C1893" t="n">
-        <v>522.3190861104064</v>
+        <v>522.3190861104063</v>
       </c>
     </row>
     <row r="1894">
@@ -21260,7 +21260,7 @@
         <v>458</v>
       </c>
       <c r="C1894" t="n">
-        <v>500.5248481937968</v>
+        <v>500.5248481937969</v>
       </c>
     </row>
     <row r="1895">
@@ -21271,7 +21271,7 @@
         <v>453</v>
       </c>
       <c r="C1895" t="n">
-        <v>468.1507327442183</v>
+        <v>468.1507327442184</v>
       </c>
     </row>
     <row r="1896">
@@ -21304,7 +21304,7 @@
         <v>604</v>
       </c>
       <c r="C1898" t="n">
-        <v>519.6492896916481</v>
+        <v>519.6492896916482</v>
       </c>
     </row>
     <row r="1899">
@@ -21337,7 +21337,7 @@
         <v>354</v>
       </c>
       <c r="C1901" t="n">
-        <v>354.6372389075449</v>
+        <v>354.6372389075451</v>
       </c>
     </row>
     <row r="1902">
@@ -21425,7 +21425,7 @@
         <v>170</v>
       </c>
       <c r="C1909" t="n">
-        <v>172.7952641629097</v>
+        <v>172.7952641629098</v>
       </c>
     </row>
     <row r="1910">
@@ -21480,7 +21480,7 @@
         <v>577</v>
       </c>
       <c r="C1914" t="n">
-        <v>564.9163337682105</v>
+        <v>564.9163337682106</v>
       </c>
     </row>
     <row r="1915">
@@ -21634,7 +21634,7 @@
         <v>416</v>
       </c>
       <c r="C1928" t="n">
-        <v>358.2947577085857</v>
+        <v>358.2947577085858</v>
       </c>
     </row>
     <row r="1929">
@@ -21722,7 +21722,7 @@
         <v>211</v>
       </c>
       <c r="C1936" t="n">
-        <v>183.2861054632125</v>
+        <v>183.2861054632124</v>
       </c>
     </row>
     <row r="1937">
@@ -21733,7 +21733,7 @@
         <v>334</v>
       </c>
       <c r="C1937" t="n">
-        <v>294.3790496522402</v>
+        <v>294.3790496522401</v>
       </c>
     </row>
     <row r="1938">
@@ -21788,7 +21788,7 @@
         <v>489</v>
       </c>
       <c r="C1942" t="n">
-        <v>408.5802235052661</v>
+        <v>408.580223505266</v>
       </c>
     </row>
     <row r="1943">
@@ -21810,7 +21810,7 @@
         <v>543</v>
       </c>
       <c r="C1944" t="n">
-        <v>450.6457492522771</v>
+        <v>450.6457492522773</v>
       </c>
     </row>
     <row r="1945">
@@ -21821,7 +21821,7 @@
         <v>589</v>
       </c>
       <c r="C1945" t="n">
-        <v>487.9093617516695</v>
+        <v>487.9093617516696</v>
       </c>
     </row>
     <row r="1946">
@@ -21843,7 +21843,7 @@
         <v>462</v>
       </c>
       <c r="C1947" t="n">
-        <v>484.7230678259691</v>
+        <v>484.7230678259692</v>
       </c>
     </row>
     <row r="1948">
@@ -21865,7 +21865,7 @@
         <v>394</v>
       </c>
       <c r="C1949" t="n">
-        <v>378.5746378536216</v>
+        <v>378.5746378536215</v>
       </c>
     </row>
     <row r="1950">
@@ -21920,7 +21920,7 @@
         <v>109</v>
       </c>
       <c r="C1954" t="n">
-        <v>110.8206526337619</v>
+        <v>110.820652633762</v>
       </c>
     </row>
     <row r="1955">
@@ -21942,7 +21942,7 @@
         <v>85</v>
       </c>
       <c r="C1956" t="n">
-        <v>88.34285446034136</v>
+        <v>88.34285446034133</v>
       </c>
     </row>
     <row r="1957">
@@ -22019,7 +22019,7 @@
         <v>673</v>
       </c>
       <c r="C1963" t="n">
-        <v>574.559749950685</v>
+        <v>574.5597499506849</v>
       </c>
     </row>
     <row r="1964">
@@ -22107,7 +22107,7 @@
         <v>333</v>
       </c>
       <c r="C1971" t="n">
-        <v>460.946134648155</v>
+        <v>460.9461346481549</v>
       </c>
     </row>
     <row r="1972">
@@ -22118,7 +22118,7 @@
         <v>377</v>
       </c>
       <c r="C1972" t="n">
-        <v>393.3609750174188</v>
+        <v>393.3609750174189</v>
       </c>
     </row>
     <row r="1973">
@@ -22129,7 +22129,7 @@
         <v>400</v>
       </c>
       <c r="C1973" t="n">
-        <v>327.7339937718566</v>
+        <v>327.7339937718567</v>
       </c>
     </row>
     <row r="1974">
@@ -22173,7 +22173,7 @@
         <v>173</v>
       </c>
       <c r="C1977" t="n">
-        <v>171.275107448133</v>
+        <v>171.2751074481329</v>
       </c>
     </row>
     <row r="1978">
@@ -22184,7 +22184,7 @@
         <v>148</v>
       </c>
       <c r="C1978" t="n">
-        <v>131.0576677718531</v>
+        <v>131.0576677718532</v>
       </c>
     </row>
     <row r="1979">
@@ -22217,7 +22217,7 @@
         <v>122</v>
       </c>
       <c r="C1981" t="n">
-        <v>181.1644165083752</v>
+        <v>181.1644165083753</v>
       </c>
     </row>
     <row r="1982">
@@ -22228,7 +22228,7 @@
         <v>335</v>
       </c>
       <c r="C1982" t="n">
-        <v>328.2024866903508</v>
+        <v>328.2024866903507</v>
       </c>
     </row>
     <row r="1983">
@@ -22283,7 +22283,7 @@
         <v>653</v>
       </c>
       <c r="C1987" t="n">
-        <v>599.4894734960536</v>
+        <v>599.4894734960535</v>
       </c>
     </row>
     <row r="1988">
@@ -22316,7 +22316,7 @@
         <v>419</v>
       </c>
       <c r="C1990" t="n">
-        <v>480.3122211504297</v>
+        <v>480.3122211504296</v>
       </c>
     </row>
     <row r="1991">
@@ -22360,7 +22360,7 @@
         <v>517</v>
       </c>
       <c r="C1994" t="n">
-        <v>515.9281636680494</v>
+        <v>515.9281636680495</v>
       </c>
     </row>
     <row r="1995">
@@ -22371,7 +22371,7 @@
         <v>499</v>
       </c>
       <c r="C1995" t="n">
-        <v>517.906901604524</v>
+        <v>517.9069016045239</v>
       </c>
     </row>
     <row r="1996">
@@ -22514,7 +22514,7 @@
         <v>588</v>
       </c>
       <c r="C2008" t="n">
-        <v>596.4565128967045</v>
+        <v>596.4565128967043</v>
       </c>
     </row>
     <row r="2009">
@@ -22536,7 +22536,7 @@
         <v>646</v>
       </c>
       <c r="C2010" t="n">
-        <v>593.4693388907538</v>
+        <v>593.4693388907539</v>
       </c>
     </row>
     <row r="2011">
@@ -22558,7 +22558,7 @@
         <v>570</v>
       </c>
       <c r="C2012" t="n">
-        <v>553.1791639132537</v>
+        <v>553.1791639132538</v>
       </c>
     </row>
     <row r="2013">
@@ -22624,7 +22624,7 @@
         <v>463</v>
       </c>
       <c r="C2018" t="n">
-        <v>511.8822524038764</v>
+        <v>511.8822524038765</v>
       </c>
     </row>
     <row r="2019">
@@ -22701,7 +22701,7 @@
         <v>280</v>
       </c>
       <c r="C2025" t="n">
-        <v>291.5088354732897</v>
+        <v>291.5088354732896</v>
       </c>
     </row>
     <row r="2026">
@@ -22756,7 +22756,7 @@
         <v>306</v>
       </c>
       <c r="C2030" t="n">
-        <v>327.6970656429619</v>
+        <v>327.6970656429618</v>
       </c>
     </row>
     <row r="2031">
@@ -22811,7 +22811,7 @@
         <v>640</v>
       </c>
       <c r="C2035" t="n">
-        <v>549.6449574242488</v>
+        <v>549.6449574242489</v>
       </c>
     </row>
     <row r="2036">
@@ -22822,7 +22822,7 @@
         <v>532</v>
       </c>
       <c r="C2036" t="n">
-        <v>554.578215237174</v>
+        <v>554.5782152371742</v>
       </c>
     </row>
     <row r="2037">
@@ -22899,7 +22899,7 @@
         <v>421</v>
       </c>
       <c r="C2043" t="n">
-        <v>550.9484975150134</v>
+        <v>550.9484975150135</v>
       </c>
     </row>
     <row r="2044">
@@ -22910,7 +22910,7 @@
         <v>327</v>
       </c>
       <c r="C2044" t="n">
-        <v>465.5956811758078</v>
+        <v>465.5956811758079</v>
       </c>
     </row>
     <row r="2045">
@@ -22921,7 +22921,7 @@
         <v>399</v>
       </c>
       <c r="C2045" t="n">
-        <v>399.1841953681412</v>
+        <v>399.1841953681413</v>
       </c>
     </row>
     <row r="2046">
@@ -23020,7 +23020,7 @@
         <v>200</v>
       </c>
       <c r="C2054" t="n">
-        <v>205.5921963656498</v>
+        <v>205.5921963656499</v>
       </c>
     </row>
     <row r="2055">
@@ -23097,7 +23097,7 @@
         <v>529</v>
       </c>
       <c r="C2061" t="n">
-        <v>484.3197618478153</v>
+        <v>484.3197618478154</v>
       </c>
     </row>
     <row r="2062">
@@ -23130,7 +23130,7 @@
         <v>518</v>
       </c>
       <c r="C2064" t="n">
-        <v>452.0606343108523</v>
+        <v>452.0606343108524</v>
       </c>
     </row>
     <row r="2065">
@@ -23262,7 +23262,7 @@
         <v>74</v>
       </c>
       <c r="C2076" t="n">
-        <v>81.47076586490022</v>
+        <v>81.4707658649002</v>
       </c>
     </row>
     <row r="2077">
@@ -23284,7 +23284,7 @@
         <v>304</v>
       </c>
       <c r="C2078" t="n">
-        <v>328.3112054426521</v>
+        <v>328.3112054426519</v>
       </c>
     </row>
     <row r="2079">
@@ -23328,7 +23328,7 @@
         <v>579</v>
       </c>
       <c r="C2082" t="n">
-        <v>590.4554692745992</v>
+        <v>590.4554692745993</v>
       </c>
     </row>
     <row r="2083">
@@ -23339,7 +23339,7 @@
         <v>579</v>
       </c>
       <c r="C2083" t="n">
-        <v>585.5251864302751</v>
+        <v>585.525186430275</v>
       </c>
     </row>
     <row r="2084">
@@ -23394,7 +23394,7 @@
         <v>466</v>
       </c>
       <c r="C2088" t="n">
-        <v>474.3812112643488</v>
+        <v>474.3812112643487</v>
       </c>
     </row>
     <row r="2089">
@@ -23405,7 +23405,7 @@
         <v>526</v>
       </c>
       <c r="C2089" t="n">
-        <v>493.3757683989791</v>
+        <v>493.375768398979</v>
       </c>
     </row>
     <row r="2090">
@@ -23570,7 +23570,7 @@
         <v>633</v>
       </c>
       <c r="C2104" t="n">
-        <v>586.3524075927958</v>
+        <v>586.3524075927957</v>
       </c>
     </row>
     <row r="2105">
@@ -23592,7 +23592,7 @@
         <v>609</v>
       </c>
       <c r="C2106" t="n">
-        <v>579.0988815816902</v>
+        <v>579.0988815816901</v>
       </c>
     </row>
     <row r="2107">
@@ -23614,7 +23614,7 @@
         <v>589</v>
       </c>
       <c r="C2108" t="n">
-        <v>548.7784412082959</v>
+        <v>548.778441208296</v>
       </c>
     </row>
     <row r="2109">
@@ -23669,7 +23669,7 @@
         <v>530</v>
       </c>
       <c r="C2113" t="n">
-        <v>509.4251594121288</v>
+        <v>509.4251594121289</v>
       </c>
     </row>
     <row r="2114">
@@ -23702,7 +23702,7 @@
         <v>449</v>
       </c>
       <c r="C2116" t="n">
-        <v>415.7443715757964</v>
+        <v>415.7443715757965</v>
       </c>
     </row>
     <row r="2117">
@@ -23713,7 +23713,7 @@
         <v>375</v>
       </c>
       <c r="C2117" t="n">
-        <v>381.6016482485008</v>
+        <v>381.6016482485009</v>
       </c>
     </row>
     <row r="2118">
@@ -23757,7 +23757,7 @@
         <v>223</v>
       </c>
       <c r="C2121" t="n">
-        <v>245.5953134028675</v>
+        <v>245.5953134028676</v>
       </c>
     </row>
     <row r="2122">
@@ -23845,7 +23845,7 @@
         <v>576</v>
       </c>
       <c r="C2129" t="n">
-        <v>587.6493107719397</v>
+        <v>587.6493107719396</v>
       </c>
     </row>
     <row r="2130">
@@ -23889,7 +23889,7 @@
         <v>482</v>
       </c>
       <c r="C2133" t="n">
-        <v>532.5438238345033</v>
+        <v>532.5438238345034</v>
       </c>
     </row>
     <row r="2134">
@@ -23900,7 +23900,7 @@
         <v>398</v>
       </c>
       <c r="C2134" t="n">
-        <v>487.3272339571743</v>
+        <v>487.3272339571744</v>
       </c>
     </row>
     <row r="2135">
@@ -23944,7 +23944,7 @@
         <v>527</v>
       </c>
       <c r="C2138" t="n">
-        <v>516.4587297985912</v>
+        <v>516.4587297985911</v>
       </c>
     </row>
     <row r="2139">
@@ -23955,7 +23955,7 @@
         <v>383</v>
       </c>
       <c r="C2139" t="n">
-        <v>524.5091477594245</v>
+        <v>524.5091477594244</v>
       </c>
     </row>
     <row r="2140">
@@ -23966,7 +23966,7 @@
         <v>547</v>
       </c>
       <c r="C2140" t="n">
-        <v>440.4930186565353</v>
+        <v>440.4930186565354</v>
       </c>
     </row>
     <row r="2141">
@@ -24043,7 +24043,7 @@
         <v>225</v>
       </c>
       <c r="C2147" t="n">
-        <v>243.6625510361764</v>
+        <v>243.6625510361765</v>
       </c>
     </row>
     <row r="2148">
@@ -24087,7 +24087,7 @@
         <v>405</v>
       </c>
       <c r="C2151" t="n">
-        <v>449.8162939365088</v>
+        <v>449.8162939365089</v>
       </c>
     </row>
     <row r="2152">
@@ -24131,7 +24131,7 @@
         <v>556</v>
       </c>
       <c r="C2155" t="n">
-        <v>519.350876045355</v>
+        <v>519.3508760453551</v>
       </c>
     </row>
     <row r="2156">
@@ -24153,7 +24153,7 @@
         <v>510</v>
       </c>
       <c r="C2157" t="n">
-        <v>490.0055459117647</v>
+        <v>490.0055459117648</v>
       </c>
     </row>
     <row r="2158">
@@ -24241,7 +24241,7 @@
         <v>464</v>
       </c>
       <c r="C2165" t="n">
-        <v>473.2644373372685</v>
+        <v>473.2644373372684</v>
       </c>
     </row>
     <row r="2166">
@@ -24252,7 +24252,7 @@
         <v>423</v>
       </c>
       <c r="C2166" t="n">
-        <v>411.9233080144717</v>
+        <v>411.9233080144718</v>
       </c>
     </row>
     <row r="2167">
@@ -24285,7 +24285,7 @@
         <v>316</v>
       </c>
       <c r="C2169" t="n">
-        <v>342.9114044020155</v>
+        <v>342.9114044020156</v>
       </c>
     </row>
     <row r="2170">
@@ -24340,7 +24340,7 @@
         <v>179</v>
       </c>
       <c r="C2174" t="n">
-        <v>171.336824456441</v>
+        <v>171.3368244564409</v>
       </c>
     </row>
     <row r="2175">
@@ -24373,7 +24373,7 @@
         <v>292</v>
       </c>
       <c r="C2177" t="n">
-        <v>288.5025988454313</v>
+        <v>288.5025988454314</v>
       </c>
     </row>
     <row r="2178">
@@ -24560,7 +24560,7 @@
         <v>85</v>
       </c>
       <c r="C2194" t="n">
-        <v>90.18326131872085</v>
+        <v>90.18326131872084</v>
       </c>
     </row>
     <row r="2195">
@@ -24626,7 +24626,7 @@
         <v>489</v>
       </c>
       <c r="C2200" t="n">
-        <v>471.5183700644441</v>
+        <v>471.5183700644442</v>
       </c>
     </row>
     <row r="2201">
@@ -24659,7 +24659,7 @@
         <v>587</v>
       </c>
       <c r="C2203" t="n">
-        <v>553.6679896107501</v>
+        <v>553.6679896107503</v>
       </c>
     </row>
     <row r="2204">
@@ -24692,7 +24692,7 @@
         <v>518</v>
       </c>
       <c r="C2206" t="n">
-        <v>486.3529600935478</v>
+        <v>486.3529600935479</v>
       </c>
     </row>
     <row r="2207">
@@ -24747,7 +24747,7 @@
         <v>483</v>
       </c>
       <c r="C2211" t="n">
-        <v>437.3138860957999</v>
+        <v>437.3138860958001</v>
       </c>
     </row>
     <row r="2212">
@@ -24780,7 +24780,7 @@
         <v>330</v>
       </c>
       <c r="C2214" t="n">
-        <v>330.2294083312503</v>
+        <v>330.2294083312502</v>
       </c>
     </row>
     <row r="2215">
@@ -24813,7 +24813,7 @@
         <v>157</v>
       </c>
       <c r="C2217" t="n">
-        <v>165.5439347994386</v>
+        <v>165.5439347994385</v>
       </c>
     </row>
     <row r="2218">
@@ -24846,7 +24846,7 @@
         <v>106</v>
       </c>
       <c r="C2220" t="n">
-        <v>97.87740936070452</v>
+        <v>97.87740936070453</v>
       </c>
     </row>
     <row r="2221">
@@ -24857,7 +24857,7 @@
         <v>128</v>
       </c>
       <c r="C2221" t="n">
-        <v>140.666683536758</v>
+        <v>140.6666835367581</v>
       </c>
     </row>
     <row r="2222">
@@ -24901,7 +24901,7 @@
         <v>388</v>
       </c>
       <c r="C2225" t="n">
-        <v>399.950115569213</v>
+        <v>399.9501155692129</v>
       </c>
     </row>
     <row r="2226">
@@ -24956,7 +24956,7 @@
         <v>334</v>
       </c>
       <c r="C2230" t="n">
-        <v>368.1574434884324</v>
+        <v>368.1574434884325</v>
       </c>
     </row>
     <row r="2231">
@@ -24978,7 +24978,7 @@
         <v>331</v>
       </c>
       <c r="C2232" t="n">
-        <v>352.6450783058069</v>
+        <v>352.6450783058068</v>
       </c>
     </row>
     <row r="2233">
@@ -25077,7 +25077,7 @@
         <v>112</v>
       </c>
       <c r="C2241" t="n">
-        <v>123.1360367601604</v>
+        <v>123.1360367601605</v>
       </c>
     </row>
     <row r="2242">
@@ -25132,7 +25132,7 @@
         <v>249</v>
       </c>
       <c r="C2246" t="n">
-        <v>393.9252942743128</v>
+        <v>393.9252942743127</v>
       </c>
     </row>
     <row r="2247">
@@ -25220,7 +25220,7 @@
         <v>525</v>
       </c>
       <c r="C2254" t="n">
-        <v>495.2940384015118</v>
+        <v>495.2940384015117</v>
       </c>
     </row>
     <row r="2255">
@@ -25253,7 +25253,7 @@
         <v>281</v>
       </c>
       <c r="C2257" t="n">
-        <v>574.3433111789474</v>
+        <v>574.3433111789473</v>
       </c>
     </row>
     <row r="2258">
@@ -25275,7 +25275,7 @@
         <v>383</v>
       </c>
       <c r="C2259" t="n">
-        <v>423.2030809816199</v>
+        <v>423.20308098162</v>
       </c>
     </row>
     <row r="2260">
@@ -25561,7 +25561,7 @@
         <v>410</v>
       </c>
       <c r="C2285" t="n">
-        <v>379.5314141789622</v>
+        <v>379.531414178962</v>
       </c>
     </row>
     <row r="2286">
@@ -25605,7 +25605,7 @@
         <v>304</v>
       </c>
       <c r="C2289" t="n">
-        <v>333.9683787786432</v>
+        <v>333.9683787786431</v>
       </c>
     </row>
     <row r="2290">
@@ -25660,7 +25660,7 @@
         <v>183</v>
       </c>
       <c r="C2294" t="n">
-        <v>160.6080875064032</v>
+        <v>160.6080875064033</v>
       </c>
     </row>
     <row r="2295">
@@ -25715,7 +25715,7 @@
         <v>484</v>
       </c>
       <c r="C2299" t="n">
-        <v>434.9407316692823</v>
+        <v>434.9407316692824</v>
       </c>
     </row>
     <row r="2300">
@@ -25748,7 +25748,7 @@
         <v>469</v>
       </c>
       <c r="C2302" t="n">
-        <v>489.0116295814559</v>
+        <v>489.011629581456</v>
       </c>
     </row>
     <row r="2303">
@@ -25781,7 +25781,7 @@
         <v>583</v>
       </c>
       <c r="C2305" t="n">
-        <v>501.6172120543311</v>
+        <v>501.6172120543312</v>
       </c>
     </row>
     <row r="2306">
@@ -25803,7 +25803,7 @@
         <v>141</v>
       </c>
       <c r="C2307" t="n">
-        <v>456.4837234341314</v>
+        <v>456.4837234341315</v>
       </c>
     </row>
     <row r="2308">
@@ -25836,7 +25836,7 @@
         <v>328</v>
       </c>
       <c r="C2310" t="n">
-        <v>323.4136853291635</v>
+        <v>323.4136853291636</v>
       </c>
     </row>
     <row r="2311">
@@ -25847,7 +25847,7 @@
         <v>268</v>
       </c>
       <c r="C2311" t="n">
-        <v>257.0603373418226</v>
+        <v>257.0603373418225</v>
       </c>
     </row>
     <row r="2312">
@@ -25935,7 +25935,7 @@
         <v>353</v>
       </c>
       <c r="C2319" t="n">
-        <v>368.0808457991992</v>
+        <v>368.0808457991993</v>
       </c>
     </row>
     <row r="2320">
@@ -25968,7 +25968,7 @@
         <v>560</v>
       </c>
       <c r="C2322" t="n">
-        <v>476.9350459622329</v>
+        <v>476.9350459622328</v>
       </c>
     </row>
     <row r="2323">
@@ -26012,7 +26012,7 @@
         <v>486</v>
       </c>
       <c r="C2326" t="n">
-        <v>476.3062091973578</v>
+        <v>476.3062091973579</v>
       </c>
     </row>
     <row r="2327">
@@ -26056,7 +26056,7 @@
         <v>284</v>
       </c>
       <c r="C2330" t="n">
-        <v>575.7685369961265</v>
+        <v>575.7685369961266</v>
       </c>
     </row>
     <row r="2331">
@@ -26232,7 +26232,7 @@
         <v>415</v>
       </c>
       <c r="C2346" t="n">
-        <v>399.0640109531333</v>
+        <v>399.0640109531332</v>
       </c>
     </row>
     <row r="2347">
@@ -26265,7 +26265,7 @@
         <v>380</v>
       </c>
       <c r="C2349" t="n">
-        <v>422.2318377440916</v>
+        <v>422.2318377440915</v>
       </c>
     </row>
     <row r="2350">
@@ -26276,7 +26276,7 @@
         <v>353</v>
       </c>
       <c r="C2350" t="n">
-        <v>361.727366528104</v>
+        <v>361.7273665281039</v>
       </c>
     </row>
     <row r="2351">
@@ -26342,7 +26342,7 @@
         <v>319</v>
       </c>
       <c r="C2356" t="n">
-        <v>360.2699514063763</v>
+        <v>360.2699514063762</v>
       </c>
     </row>
     <row r="2357">
@@ -26353,7 +26353,7 @@
         <v>255</v>
       </c>
       <c r="C2357" t="n">
-        <v>278.3738609881095</v>
+        <v>278.3738609881096</v>
       </c>
     </row>
     <row r="2358">
@@ -26419,7 +26419,7 @@
         <v>99</v>
       </c>
       <c r="C2363" t="n">
-        <v>105.9766221969721</v>
+        <v>105.9766221969722</v>
       </c>
     </row>
     <row r="2364">
@@ -26474,7 +26474,7 @@
         <v>436</v>
       </c>
       <c r="C2368" t="n">
-        <v>412.7785741501695</v>
+        <v>412.7785741501696</v>
       </c>
     </row>
     <row r="2369">
@@ -26507,7 +26507,7 @@
         <v>607</v>
       </c>
       <c r="C2371" t="n">
-        <v>598.7664694120585</v>
+        <v>598.7664694120584</v>
       </c>
     </row>
     <row r="2372">
@@ -26518,7 +26518,7 @@
         <v>630</v>
       </c>
       <c r="C2372" t="n">
-        <v>586.1368989902817</v>
+        <v>586.1368989902816</v>
       </c>
     </row>
     <row r="2373">
@@ -26760,7 +26760,7 @@
         <v>559</v>
       </c>
       <c r="C2394" t="n">
-        <v>555.2031503881741</v>
+        <v>555.203150388174</v>
       </c>
     </row>
     <row r="2395">
@@ -26793,7 +26793,7 @@
         <v>519</v>
       </c>
       <c r="C2397" t="n">
-        <v>551.059703864506</v>
+        <v>551.0597038645061</v>
       </c>
     </row>
     <row r="2398">
@@ -26870,7 +26870,7 @@
         <v>463</v>
       </c>
       <c r="C2404" t="n">
-        <v>483.6040491872376</v>
+        <v>483.6040491872377</v>
       </c>
     </row>
     <row r="2405">
@@ -26947,7 +26947,7 @@
         <v>234</v>
       </c>
       <c r="C2411" t="n">
-        <v>220.9271313211612</v>
+        <v>220.9271313211613</v>
       </c>
     </row>
     <row r="2412">
@@ -26991,7 +26991,7 @@
         <v>175</v>
       </c>
       <c r="C2415" t="n">
-        <v>164.2794408570587</v>
+        <v>164.2794408570588</v>
       </c>
     </row>
     <row r="2416">
@@ -27035,7 +27035,7 @@
         <v>416</v>
       </c>
       <c r="C2419" t="n">
-        <v>409.5166132581516</v>
+        <v>409.5166132581515</v>
       </c>
     </row>
     <row r="2420">
@@ -27090,7 +27090,7 @@
         <v>135</v>
       </c>
       <c r="C2424" t="n">
-        <v>356.2841280875187</v>
+        <v>356.2841280875188</v>
       </c>
     </row>
     <row r="2425">
@@ -27134,7 +27134,7 @@
         <v>203</v>
       </c>
       <c r="C2428" t="n">
-        <v>243.0641955306826</v>
+        <v>243.0641955306827</v>
       </c>
     </row>
     <row r="2429">
@@ -27211,7 +27211,7 @@
         <v>81</v>
       </c>
       <c r="C2435" t="n">
-        <v>93.53925730295612</v>
+        <v>93.5392573029561</v>
       </c>
     </row>
     <row r="2436">
@@ -27244,7 +27244,7 @@
         <v>295</v>
       </c>
       <c r="C2438" t="n">
-        <v>393.2957561083427</v>
+        <v>393.2957561083429</v>
       </c>
     </row>
     <row r="2439">
@@ -27277,7 +27277,7 @@
         <v>496</v>
       </c>
       <c r="C2441" t="n">
-        <v>580.2627513765742</v>
+        <v>580.2627513765741</v>
       </c>
     </row>
     <row r="2442">
@@ -27420,7 +27420,7 @@
         <v>325</v>
       </c>
       <c r="C2454" t="n">
-        <v>287.4501662859567</v>
+        <v>287.4501662859568</v>
       </c>
     </row>
     <row r="2455">
@@ -27552,7 +27552,7 @@
         <v>604</v>
       </c>
       <c r="C2466" t="n">
-        <v>599.4086345177936</v>
+        <v>599.4086345177935</v>
       </c>
     </row>
     <row r="2467">
@@ -27618,7 +27618,7 @@
         <v>454</v>
       </c>
       <c r="C2472" t="n">
-        <v>484.3441564100047</v>
+        <v>484.3441564100048</v>
       </c>
     </row>
     <row r="2473">
@@ -27640,7 +27640,7 @@
         <v>525</v>
       </c>
       <c r="C2474" t="n">
-        <v>526.0037422842369</v>
+        <v>526.0037422842368</v>
       </c>
     </row>
     <row r="2475">
@@ -27805,7 +27805,7 @@
         <v>532</v>
       </c>
       <c r="C2489" t="n">
-        <v>580.4471942048532</v>
+        <v>580.4471942048531</v>
       </c>
     </row>
     <row r="2490">
@@ -27860,7 +27860,7 @@
         <v>426</v>
       </c>
       <c r="C2494" t="n">
-        <v>460.6174632217796</v>
+        <v>460.6174632217797</v>
       </c>
     </row>
     <row r="2495">
@@ -27893,7 +27893,7 @@
         <v>503</v>
       </c>
       <c r="C2497" t="n">
-        <v>532.8062364809803</v>
+        <v>532.8062364809801</v>
       </c>
     </row>
     <row r="2498">
@@ -27948,7 +27948,7 @@
         <v>381</v>
       </c>
       <c r="C2502" t="n">
-        <v>368.1895091377198</v>
+        <v>368.1895091377197</v>
       </c>
     </row>
     <row r="2503">
@@ -27992,7 +27992,7 @@
         <v>290</v>
       </c>
       <c r="C2506" t="n">
-        <v>303.3032582064465</v>
+        <v>303.3032582064466</v>
       </c>
     </row>
     <row r="2507">
@@ -28047,7 +28047,7 @@
         <v>167</v>
       </c>
       <c r="C2511" t="n">
-        <v>172.4292735280048</v>
+        <v>172.4292735280047</v>
       </c>
     </row>
     <row r="2512">
@@ -28058,7 +28058,7 @@
         <v>196</v>
       </c>
       <c r="C2512" t="n">
-        <v>221.2564342204172</v>
+        <v>221.2564342204171</v>
       </c>
     </row>
     <row r="2513">
@@ -28069,7 +28069,7 @@
         <v>262</v>
       </c>
       <c r="C2513" t="n">
-        <v>271.6291169622389</v>
+        <v>271.629116962239</v>
       </c>
     </row>
     <row r="2514">
@@ -28157,7 +28157,7 @@
         <v>428</v>
       </c>
       <c r="C2521" t="n">
-        <v>426.5716547792623</v>
+        <v>426.5716547792624</v>
       </c>
     </row>
     <row r="2522">
@@ -28168,7 +28168,7 @@
         <v>371</v>
       </c>
       <c r="C2522" t="n">
-        <v>428.1580191888165</v>
+        <v>428.1580191888166</v>
       </c>
     </row>
     <row r="2523">
@@ -28267,7 +28267,7 @@
         <v>84</v>
       </c>
       <c r="C2531" t="n">
-        <v>86.5803947301677</v>
+        <v>86.58039473016768</v>
       </c>
     </row>
     <row r="2532">
@@ -28278,7 +28278,7 @@
         <v>64</v>
       </c>
       <c r="C2532" t="n">
-        <v>95.14607505786508</v>
+        <v>95.14607505786506</v>
       </c>
     </row>
     <row r="2533">
@@ -28355,7 +28355,7 @@
         <v>557</v>
       </c>
       <c r="C2539" t="n">
-        <v>595.928887246277</v>
+        <v>595.9288872462769</v>
       </c>
     </row>
     <row r="2540">
@@ -28388,7 +28388,7 @@
         <v>387</v>
       </c>
       <c r="C2542" t="n">
-        <v>451.4680900766651</v>
+        <v>451.4680900766652</v>
       </c>
     </row>
     <row r="2543">
@@ -28487,7 +28487,7 @@
         <v>217</v>
       </c>
       <c r="C2551" t="n">
-        <v>223.1319897358553</v>
+        <v>223.1319897358552</v>
       </c>
     </row>
     <row r="2552">
@@ -28663,7 +28663,7 @@
         <v>416</v>
       </c>
       <c r="C2567" t="n">
-        <v>444.0940647834114</v>
+        <v>444.0940647834115</v>
       </c>
     </row>
     <row r="2568">
@@ -28949,7 +28949,7 @@
         <v>496</v>
       </c>
       <c r="C2593" t="n">
-        <v>452.4581353344659</v>
+        <v>452.458135334466</v>
       </c>
     </row>
     <row r="2594">
@@ -28960,7 +28960,7 @@
         <v>603</v>
       </c>
       <c r="C2594" t="n">
-        <v>515.3741618988835</v>
+        <v>515.3741618988834</v>
       </c>
     </row>
     <row r="2595">
@@ -29037,7 +29037,7 @@
         <v>258</v>
       </c>
       <c r="C2601" t="n">
-        <v>246.1724471665058</v>
+        <v>246.1724471665057</v>
       </c>
     </row>
     <row r="2602">
@@ -29048,7 +29048,7 @@
         <v>200</v>
       </c>
       <c r="C2602" t="n">
-        <v>206.9346235884649</v>
+        <v>206.9346235884648</v>
       </c>
     </row>
     <row r="2603">
@@ -29356,7 +29356,7 @@
         <v>195</v>
       </c>
       <c r="C2630" t="n">
-        <v>217.9228589629153</v>
+        <v>217.9228589629154</v>
       </c>
     </row>
     <row r="2631">
@@ -29422,7 +29422,7 @@
         <v>472</v>
       </c>
       <c r="C2636" t="n">
-        <v>452.1426439490627</v>
+        <v>452.1426439490629</v>
       </c>
     </row>
     <row r="2637">
@@ -29455,7 +29455,7 @@
         <v>403</v>
       </c>
       <c r="C2639" t="n">
-        <v>422.6550285382349</v>
+        <v>422.6550285382348</v>
       </c>
     </row>
     <row r="2640">
@@ -29532,7 +29532,7 @@
         <v>241</v>
       </c>
       <c r="C2646" t="n">
-        <v>272.8249338296491</v>
+        <v>272.824933829649</v>
       </c>
     </row>
     <row r="2647">
@@ -29576,7 +29576,7 @@
         <v>102</v>
       </c>
       <c r="C2650" t="n">
-        <v>90.1126886331907</v>
+        <v>90.11268863319069</v>
       </c>
     </row>
     <row r="2651">
@@ -29587,7 +29587,7 @@
         <v>77</v>
       </c>
       <c r="C2651" t="n">
-        <v>88.43708187905322</v>
+        <v>88.43708187905321</v>
       </c>
     </row>
     <row r="2652">
@@ -29664,7 +29664,7 @@
         <v>479</v>
       </c>
       <c r="C2658" t="n">
-        <v>590.0635908642248</v>
+        <v>590.0635908642247</v>
       </c>
     </row>
     <row r="2659">
@@ -29686,7 +29686,7 @@
         <v>533</v>
       </c>
       <c r="C2660" t="n">
-        <v>551.8976340235997</v>
+        <v>551.8976340235998</v>
       </c>
     </row>
     <row r="2661">
@@ -29741,7 +29741,7 @@
         <v>497</v>
       </c>
       <c r="C2665" t="n">
-        <v>468.9350569557212</v>
+        <v>468.9350569557213</v>
       </c>
     </row>
     <row r="2666">
@@ -29829,7 +29829,7 @@
         <v>182</v>
       </c>
       <c r="C2673" t="n">
-        <v>168.7316161411433</v>
+        <v>168.7316161411434</v>
       </c>
     </row>
     <row r="2674">
@@ -29884,7 +29884,7 @@
         <v>325</v>
       </c>
       <c r="C2678" t="n">
-        <v>322.7577833786647</v>
+        <v>322.7577833786646</v>
       </c>
     </row>
     <row r="2679">
@@ -29895,7 +29895,7 @@
         <v>475</v>
       </c>
       <c r="C2679" t="n">
-        <v>470.9453919533032</v>
+        <v>470.9453919533031</v>
       </c>
     </row>
     <row r="2680">
@@ -29917,7 +29917,7 @@
         <v>645</v>
       </c>
       <c r="C2681" t="n">
-        <v>587.9729868595405</v>
+        <v>587.9729868595406</v>
       </c>
     </row>
     <row r="2682">
@@ -29928,7 +29928,7 @@
         <v>527</v>
       </c>
       <c r="C2682" t="n">
-        <v>595.4040830405461</v>
+        <v>595.4040830405462</v>
       </c>
     </row>
     <row r="2683">
@@ -30005,7 +30005,7 @@
         <v>504</v>
       </c>
       <c r="C2689" t="n">
-        <v>457.7952070866417</v>
+        <v>457.7952070866416</v>
       </c>
     </row>
     <row r="2690">
@@ -30192,7 +30192,7 @@
         <v>527</v>
       </c>
       <c r="C2706" t="n">
-        <v>576.084956675902</v>
+        <v>576.0849566759019</v>
       </c>
     </row>
     <row r="2707">
@@ -30258,7 +30258,7 @@
         <v>519</v>
       </c>
       <c r="C2712" t="n">
-        <v>462.8620635002923</v>
+        <v>462.8620635002924</v>
       </c>
     </row>
     <row r="2713">
@@ -30269,7 +30269,7 @@
         <v>546</v>
       </c>
       <c r="C2713" t="n">
-        <v>522.2611147296598</v>
+        <v>522.2611147296599</v>
       </c>
     </row>
     <row r="2714">
@@ -30335,7 +30335,7 @@
         <v>331</v>
       </c>
       <c r="C2719" t="n">
-        <v>330.4808817317621</v>
+        <v>330.480881731762</v>
       </c>
     </row>
     <row r="2720">
@@ -30423,7 +30423,7 @@
         <v>466</v>
       </c>
       <c r="C2727" t="n">
-        <v>453.7145733443597</v>
+        <v>453.7145733443598</v>
       </c>
     </row>
     <row r="2728">
@@ -30467,7 +30467,7 @@
         <v>608</v>
       </c>
       <c r="C2731" t="n">
-        <v>577.4487751598807</v>
+        <v>577.4487751598808</v>
       </c>
     </row>
     <row r="2732">
@@ -30489,7 +30489,7 @@
         <v>459</v>
       </c>
       <c r="C2733" t="n">
-        <v>524.3881922498982</v>
+        <v>524.3881922498983</v>
       </c>
     </row>
     <row r="2734">
@@ -30500,7 +30500,7 @@
         <v>477</v>
       </c>
       <c r="C2734" t="n">
-        <v>466.007661385594</v>
+        <v>466.0076613855939</v>
       </c>
     </row>
     <row r="2735">
@@ -30566,7 +30566,7 @@
         <v>581</v>
       </c>
       <c r="C2740" t="n">
-        <v>505.3543373057906</v>
+        <v>505.3543373057905</v>
       </c>
     </row>
     <row r="2741">
@@ -30610,7 +30610,7 @@
         <v>423</v>
       </c>
       <c r="C2744" t="n">
-        <v>368.791917834966</v>
+        <v>368.7919178349659</v>
       </c>
     </row>
     <row r="2745">
@@ -30665,7 +30665,7 @@
         <v>222</v>
       </c>
       <c r="C2749" t="n">
-        <v>255.7379331152888</v>
+        <v>255.7379331152889</v>
       </c>
     </row>
     <row r="2750">
@@ -30731,7 +30731,7 @@
         <v>448</v>
       </c>
       <c r="C2755" t="n">
-        <v>416.312755587256</v>
+        <v>416.3127555872561</v>
       </c>
     </row>
     <row r="2756">
@@ -30775,7 +30775,7 @@
         <v>424</v>
       </c>
       <c r="C2759" t="n">
-        <v>422.3827305270131</v>
+        <v>422.382730527013</v>
       </c>
     </row>
     <row r="2760">
@@ -30786,7 +30786,7 @@
         <v>433</v>
       </c>
       <c r="C2760" t="n">
-        <v>427.7679523124349</v>
+        <v>427.767952312435</v>
       </c>
     </row>
     <row r="2761">
@@ -31039,7 +31039,7 @@
         <v>477</v>
       </c>
       <c r="C2783" t="n">
-        <v>452.4289393338818</v>
+        <v>452.4289393338819</v>
       </c>
     </row>
     <row r="2784">
@@ -31050,7 +31050,7 @@
         <v>404</v>
       </c>
       <c r="C2784" t="n">
-        <v>493.0376299826729</v>
+        <v>493.0376299826728</v>
       </c>
     </row>
     <row r="2785">
@@ -31061,7 +31061,7 @@
         <v>475</v>
       </c>
       <c r="C2785" t="n">
-        <v>448.4932842993144</v>
+        <v>448.4932842993145</v>
       </c>
     </row>
     <row r="2786">
@@ -31083,7 +31083,7 @@
         <v>477</v>
       </c>
       <c r="C2787" t="n">
-        <v>462.4055270618741</v>
+        <v>462.405527061874</v>
       </c>
     </row>
     <row r="2788">
@@ -31094,7 +31094,7 @@
         <v>349</v>
       </c>
       <c r="C2788" t="n">
-        <v>428.5520216324723</v>
+        <v>428.5520216324722</v>
       </c>
     </row>
     <row r="2789">
@@ -31116,7 +31116,7 @@
         <v>286</v>
       </c>
       <c r="C2790" t="n">
-        <v>274.9646446699253</v>
+        <v>274.9646446699254</v>
       </c>
     </row>
     <row r="2791">
@@ -31204,7 +31204,7 @@
         <v>312</v>
       </c>
       <c r="C2798" t="n">
-        <v>369.8223001026168</v>
+        <v>369.8223001026167</v>
       </c>
     </row>
     <row r="2799">
@@ -31237,7 +31237,7 @@
         <v>608</v>
       </c>
       <c r="C2801" t="n">
-        <v>584.127621538565</v>
+        <v>584.1276215385649</v>
       </c>
     </row>
     <row r="2802">
@@ -31281,7 +31281,7 @@
         <v>456</v>
       </c>
       <c r="C2805" t="n">
-        <v>513.5389828524935</v>
+        <v>513.5389828524936</v>
       </c>
     </row>
     <row r="2806">
@@ -31336,7 +31336,7 @@
         <v>526</v>
       </c>
       <c r="C2810" t="n">
-        <v>527.352977565052</v>
+        <v>527.3529775650521</v>
       </c>
     </row>
     <row r="2811">
@@ -31391,7 +31391,7 @@
         <v>270</v>
       </c>
       <c r="C2815" t="n">
-        <v>290.0148926465731</v>
+        <v>290.014892646573</v>
       </c>
     </row>
     <row r="2816">
@@ -31479,7 +31479,7 @@
         <v>517</v>
       </c>
       <c r="C2823" t="n">
-        <v>510.3025485673435</v>
+        <v>510.3025485673436</v>
       </c>
     </row>
     <row r="2824">
@@ -31501,7 +31501,7 @@
         <v>612</v>
       </c>
       <c r="C2825" t="n">
-        <v>595.7470812041616</v>
+        <v>595.7470812041615</v>
       </c>
     </row>
     <row r="2826">
@@ -31534,7 +31534,7 @@
         <v>551</v>
       </c>
       <c r="C2828" t="n">
-        <v>554.3160823153513</v>
+        <v>554.3160823153514</v>
       </c>
     </row>
     <row r="2829">
@@ -31556,7 +31556,7 @@
         <v>451</v>
       </c>
       <c r="C2830" t="n">
-        <v>460.1757748409734</v>
+        <v>460.1757748409735</v>
       </c>
     </row>
     <row r="2831">
@@ -31589,7 +31589,7 @@
         <v>498</v>
       </c>
       <c r="C2833" t="n">
-        <v>463.4147515772378</v>
+        <v>463.4147515772379</v>
       </c>
     </row>
     <row r="2834">
@@ -31600,7 +31600,7 @@
         <v>555</v>
       </c>
       <c r="C2834" t="n">
-        <v>515.6191915294246</v>
+        <v>515.6191915294245</v>
       </c>
     </row>
     <row r="2835">
@@ -31622,7 +31622,7 @@
         <v>439</v>
       </c>
       <c r="C2836" t="n">
-        <v>447.3829329561793</v>
+        <v>447.3829329561792</v>
       </c>
     </row>
     <row r="2837">
@@ -31677,7 +31677,7 @@
         <v>292</v>
       </c>
       <c r="C2841" t="n">
-        <v>269.414468191295</v>
+        <v>269.4144681912951</v>
       </c>
     </row>
     <row r="2842">
@@ -31765,7 +31765,7 @@
         <v>548</v>
       </c>
       <c r="C2849" t="n">
-        <v>571.4589073819573</v>
+        <v>571.4589073819571</v>
       </c>
     </row>
     <row r="2850">
@@ -31776,7 +31776,7 @@
         <v>572</v>
       </c>
       <c r="C2850" t="n">
-        <v>535.6851170717786</v>
+        <v>535.6851170717787</v>
       </c>
     </row>
     <row r="2851">
@@ -31787,7 +31787,7 @@
         <v>568</v>
       </c>
       <c r="C2851" t="n">
-        <v>591.8605961167736</v>
+        <v>591.8605961167738</v>
       </c>
     </row>
     <row r="2852">
@@ -31864,7 +31864,7 @@
         <v>592</v>
       </c>
       <c r="C2858" t="n">
-        <v>523.7876314005479</v>
+        <v>523.7876314005481</v>
       </c>
     </row>
     <row r="2859">
@@ -31908,7 +31908,7 @@
         <v>363</v>
       </c>
       <c r="C2862" t="n">
-        <v>376.1101487343053</v>
+        <v>376.1101487343052</v>
       </c>
     </row>
     <row r="2863">
@@ -31919,7 +31919,7 @@
         <v>355</v>
       </c>
       <c r="C2863" t="n">
-        <v>367.6642800263125</v>
+        <v>367.6642800263124</v>
       </c>
     </row>
     <row r="2864">
@@ -31930,7 +31930,7 @@
         <v>348</v>
       </c>
       <c r="C2864" t="n">
-        <v>346.3022609645392</v>
+        <v>346.3022609645393</v>
       </c>
     </row>
     <row r="2865">
@@ -32073,7 +32073,7 @@
         <v>452</v>
       </c>
       <c r="C2877" t="n">
-        <v>300.0130933028533</v>
+        <v>300.0130933028532</v>
       </c>
     </row>
     <row r="2878">
@@ -32084,7 +32084,7 @@
         <v>485</v>
       </c>
       <c r="C2878" t="n">
-        <v>428.9094024981749</v>
+        <v>428.909402498175</v>
       </c>
     </row>
     <row r="2879">
@@ -32106,7 +32106,7 @@
         <v>400</v>
       </c>
       <c r="C2880" t="n">
-        <v>431.7484842361422</v>
+        <v>431.7484842361421</v>
       </c>
     </row>
     <row r="2881">
@@ -32271,7 +32271,7 @@
         <v>474</v>
       </c>
       <c r="C2895" t="n">
-        <v>517.0798632473382</v>
+        <v>517.0798632473383</v>
       </c>
     </row>
     <row r="2896">
@@ -32326,7 +32326,7 @@
         <v>487</v>
       </c>
       <c r="C2900" t="n">
-        <v>541.7981337427432</v>
+        <v>541.7981337427434</v>
       </c>
     </row>
     <row r="2901">
@@ -32348,7 +32348,7 @@
         <v>433</v>
       </c>
       <c r="C2902" t="n">
-        <v>427.4037947402214</v>
+        <v>427.4037947402213</v>
       </c>
     </row>
     <row r="2903">
@@ -32403,7 +32403,7 @@
         <v>437</v>
       </c>
       <c r="C2907" t="n">
-        <v>455.4006732277621</v>
+        <v>455.400673227762</v>
       </c>
     </row>
     <row r="2908">
@@ -32491,7 +32491,7 @@
         <v>144</v>
       </c>
       <c r="C2915" t="n">
-        <v>149.0251222051193</v>
+        <v>149.0251222051192</v>
       </c>
     </row>
     <row r="2916">
@@ -32524,7 +32524,7 @@
         <v>348</v>
       </c>
       <c r="C2918" t="n">
-        <v>349.2415585823817</v>
+        <v>349.2415585823819</v>
       </c>
     </row>
     <row r="2919">
@@ -32546,7 +32546,7 @@
         <v>684</v>
       </c>
       <c r="C2920" t="n">
-        <v>570.9072225450618</v>
+        <v>570.9072225450617</v>
       </c>
     </row>
     <row r="2921">
@@ -32579,7 +32579,7 @@
         <v>551</v>
       </c>
       <c r="C2923" t="n">
-        <v>576.496752460817</v>
+        <v>576.4967524608171</v>
       </c>
     </row>
     <row r="2924">
@@ -32623,7 +32623,7 @@
         <v>418</v>
       </c>
       <c r="C2927" t="n">
-        <v>451.9828068281017</v>
+        <v>451.9828068281018</v>
       </c>
     </row>
     <row r="2928">
@@ -32656,7 +32656,7 @@
         <v>454</v>
       </c>
       <c r="C2930" t="n">
-        <v>476.1135473846714</v>
+        <v>476.1135473846713</v>
       </c>
     </row>
     <row r="2931">
@@ -32689,7 +32689,7 @@
         <v>341</v>
       </c>
       <c r="C2933" t="n">
-        <v>327.7673757169112</v>
+        <v>327.7673757169113</v>
       </c>
     </row>
     <row r="2934">
@@ -32854,7 +32854,7 @@
         <v>533</v>
       </c>
       <c r="C2948" t="n">
-        <v>561.7929190302154</v>
+        <v>561.7929190302153</v>
       </c>
     </row>
     <row r="2949">
@@ -32876,7 +32876,7 @@
         <v>452</v>
       </c>
       <c r="C2950" t="n">
-        <v>497.9682805334178</v>
+        <v>497.9682805334177</v>
       </c>
     </row>
     <row r="2951">
@@ -32898,7 +32898,7 @@
         <v>489</v>
       </c>
       <c r="C2952" t="n">
-        <v>450.4287832870784</v>
+        <v>450.4287832870783</v>
       </c>
     </row>
     <row r="2953">
@@ -32920,7 +32920,7 @@
         <v>556</v>
       </c>
       <c r="C2954" t="n">
-        <v>533.9921415215996</v>
+        <v>533.9921415215997</v>
       </c>
     </row>
     <row r="2955">
@@ -32931,7 +32931,7 @@
         <v>519</v>
       </c>
       <c r="C2955" t="n">
-        <v>564.6706654674284</v>
+        <v>564.6706654674285</v>
       </c>
     </row>
     <row r="2956">
@@ -32975,7 +32975,7 @@
         <v>356</v>
       </c>
       <c r="C2959" t="n">
-        <v>318.4528928156791</v>
+        <v>318.4528928156792</v>
       </c>
     </row>
     <row r="2960">
@@ -33019,7 +33019,7 @@
         <v>209</v>
       </c>
       <c r="C2963" t="n">
-        <v>210.6116003587019</v>
+        <v>210.6116003587018</v>
       </c>
     </row>
     <row r="2964">
@@ -33063,7 +33063,7 @@
         <v>510</v>
       </c>
       <c r="C2967" t="n">
-        <v>454.317230902816</v>
+        <v>454.3172309028161</v>
       </c>
     </row>
     <row r="2968">
@@ -33074,7 +33074,7 @@
         <v>577</v>
       </c>
       <c r="C2968" t="n">
-        <v>580.4561325649474</v>
+        <v>580.4561325649473</v>
       </c>
     </row>
     <row r="2969">
@@ -33107,7 +33107,7 @@
         <v>568</v>
       </c>
       <c r="C2971" t="n">
-        <v>546.3238393407343</v>
+        <v>546.3238393407344</v>
       </c>
     </row>
     <row r="2972">
@@ -33118,7 +33118,7 @@
         <v>523</v>
       </c>
       <c r="C2972" t="n">
-        <v>541.3606251527541</v>
+        <v>541.3606251527542</v>
       </c>
     </row>
     <row r="2973">
@@ -33129,7 +33129,7 @@
         <v>419</v>
       </c>
       <c r="C2973" t="n">
-        <v>506.3093166766979</v>
+        <v>506.3093166766981</v>
       </c>
     </row>
     <row r="2974">
@@ -33140,7 +33140,7 @@
         <v>382</v>
       </c>
       <c r="C2974" t="n">
-        <v>440.6266497200781</v>
+        <v>440.6266497200782</v>
       </c>
     </row>
     <row r="2975">
@@ -33151,7 +33151,7 @@
         <v>469</v>
       </c>
       <c r="C2975" t="n">
-        <v>431.2136899153293</v>
+        <v>431.2136899153292</v>
       </c>
     </row>
     <row r="2976">
@@ -33184,7 +33184,7 @@
         <v>568</v>
       </c>
       <c r="C2978" t="n">
-        <v>532.1802451198731</v>
+        <v>532.180245119873</v>
       </c>
     </row>
     <row r="2979">
@@ -33217,7 +33217,7 @@
         <v>436</v>
       </c>
       <c r="C2981" t="n">
-        <v>433.8970993501537</v>
+        <v>433.8970993501538</v>
       </c>
     </row>
     <row r="2982">
@@ -33239,7 +33239,7 @@
         <v>338</v>
       </c>
       <c r="C2983" t="n">
-        <v>365.5788858095672</v>
+        <v>365.5788858095671</v>
       </c>
     </row>
     <row r="2984">
@@ -33250,7 +33250,7 @@
         <v>382</v>
       </c>
       <c r="C2984" t="n">
-        <v>370.0127184420064</v>
+        <v>370.0127184420063</v>
       </c>
     </row>
     <row r="2985">
@@ -33371,7 +33371,7 @@
         <v>415</v>
       </c>
       <c r="C2995" t="n">
-        <v>415.5171408268902</v>
+        <v>415.5171408268903</v>
       </c>
     </row>
     <row r="2996">
@@ -33437,7 +33437,7 @@
         <v>460</v>
       </c>
       <c r="C3001" t="n">
-        <v>461.7897242975356</v>
+        <v>461.7897242975357</v>
       </c>
     </row>
     <row r="3002">
@@ -33448,7 +33448,7 @@
         <v>454</v>
       </c>
       <c r="C3002" t="n">
-        <v>442.9824748532139</v>
+        <v>442.982474853214</v>
       </c>
     </row>
     <row r="3003">
@@ -33536,7 +33536,7 @@
         <v>102</v>
       </c>
       <c r="C3010" t="n">
-        <v>95.4188599837464</v>
+        <v>95.41885998374639</v>
       </c>
     </row>
     <row r="3011">
@@ -33547,7 +33547,7 @@
         <v>99</v>
       </c>
       <c r="C3011" t="n">
-        <v>89.77740550978193</v>
+        <v>89.77740550978194</v>
       </c>
     </row>
     <row r="3012">
@@ -33624,7 +33624,7 @@
         <v>540</v>
       </c>
       <c r="C3018" t="n">
-        <v>600.3296367322414</v>
+        <v>600.3296367322415</v>
       </c>
     </row>
     <row r="3019">
@@ -33635,7 +33635,7 @@
         <v>551</v>
       </c>
       <c r="C3019" t="n">
-        <v>572.3663693014813</v>
+        <v>572.3663693014812</v>
       </c>
     </row>
     <row r="3020">
@@ -33701,7 +33701,7 @@
         <v>467</v>
       </c>
       <c r="C3025" t="n">
-        <v>480.6358041524429</v>
+        <v>480.6358041524428</v>
       </c>
     </row>
     <row r="3026">
@@ -33734,7 +33734,7 @@
         <v>374</v>
       </c>
       <c r="C3028" t="n">
-        <v>387.3971533167078</v>
+        <v>387.3971533167079</v>
       </c>
     </row>
     <row r="3029">
@@ -33866,7 +33866,7 @@
         <v>610</v>
       </c>
       <c r="C3040" t="n">
-        <v>600.2231852494738</v>
+        <v>600.2231852494737</v>
       </c>
     </row>
     <row r="3041">
@@ -33877,7 +33877,7 @@
         <v>642</v>
       </c>
       <c r="C3041" t="n">
-        <v>603.1915263431605</v>
+        <v>603.1915263431606</v>
       </c>
     </row>
     <row r="3042">
@@ -33899,7 +33899,7 @@
         <v>571</v>
       </c>
       <c r="C3043" t="n">
-        <v>590.0589046550954</v>
+        <v>590.0589046550951</v>
       </c>
     </row>
     <row r="3044">
@@ -33921,7 +33921,7 @@
         <v>425</v>
       </c>
       <c r="C3045" t="n">
-        <v>559.769542243412</v>
+        <v>559.7695422434122</v>
       </c>
     </row>
     <row r="3046">
@@ -33943,7 +33943,7 @@
         <v>446</v>
       </c>
       <c r="C3047" t="n">
-        <v>467.9995783117279</v>
+        <v>467.999578311728</v>
       </c>
     </row>
     <row r="3048">
@@ -33954,7 +33954,7 @@
         <v>419</v>
       </c>
       <c r="C3048" t="n">
-        <v>461.2869655376874</v>
+        <v>461.2869655376873</v>
       </c>
     </row>
     <row r="3049">
@@ -33976,7 +33976,7 @@
         <v>482</v>
       </c>
       <c r="C3050" t="n">
-        <v>508.3185901577479</v>
+        <v>508.318590157748</v>
       </c>
     </row>
     <row r="3051">
@@ -34119,7 +34119,7 @@
         <v>491</v>
       </c>
       <c r="C3063" t="n">
-        <v>480.5218229799955</v>
+        <v>480.5218229799954</v>
       </c>
     </row>
     <row r="3064">
@@ -34130,7 +34130,7 @@
         <v>590</v>
       </c>
       <c r="C3064" t="n">
-        <v>601.0948441784516</v>
+        <v>601.0948441784517</v>
       </c>
     </row>
     <row r="3065">
@@ -34163,7 +34163,7 @@
         <v>622</v>
       </c>
       <c r="C3067" t="n">
-        <v>569.5561748351586</v>
+        <v>569.5561748351587</v>
       </c>
     </row>
     <row r="3068">
@@ -34174,7 +34174,7 @@
         <v>556</v>
       </c>
       <c r="C3068" t="n">
-        <v>559.5230422388952</v>
+        <v>559.5230422388951</v>
       </c>
     </row>
     <row r="3069">
@@ -34196,7 +34196,7 @@
         <v>405</v>
       </c>
       <c r="C3070" t="n">
-        <v>450.5054452042765</v>
+        <v>450.5054452042764</v>
       </c>
     </row>
     <row r="3071">
@@ -34207,7 +34207,7 @@
         <v>454</v>
       </c>
       <c r="C3071" t="n">
-        <v>445.8537214760569</v>
+        <v>445.8537214760568</v>
       </c>
     </row>
     <row r="3072">
@@ -34218,7 +34218,7 @@
         <v>494</v>
       </c>
       <c r="C3072" t="n">
-        <v>470.548130725324</v>
+        <v>470.5481307253241</v>
       </c>
     </row>
     <row r="3073">
@@ -34229,7 +34229,7 @@
         <v>547</v>
       </c>
       <c r="C3073" t="n">
-        <v>506.3229896235537</v>
+        <v>506.3229896235538</v>
       </c>
     </row>
     <row r="3074">
@@ -34361,7 +34361,7 @@
         <v>209</v>
       </c>
       <c r="C3085" t="n">
-        <v>194.8906866708353</v>
+        <v>194.8906866708352</v>
       </c>
     </row>
     <row r="3086">
@@ -34394,7 +34394,7 @@
         <v>532</v>
       </c>
       <c r="C3088" t="n">
-        <v>565.5257752944291</v>
+        <v>565.525775294429</v>
       </c>
     </row>
     <row r="3089">
@@ -34405,7 +34405,7 @@
         <v>584</v>
       </c>
       <c r="C3089" t="n">
-        <v>558.1645347309704</v>
+        <v>558.1645347309706</v>
       </c>
     </row>
     <row r="3090">
@@ -34471,7 +34471,7 @@
         <v>493</v>
       </c>
       <c r="C3095" t="n">
-        <v>452.3986612020566</v>
+        <v>452.3986612020565</v>
       </c>
     </row>
     <row r="3096">
@@ -34559,7 +34559,7 @@
         <v>367</v>
       </c>
       <c r="C3103" t="n">
-        <v>423.0982199918093</v>
+        <v>423.0982199918094</v>
       </c>
     </row>
     <row r="3104">
@@ -34647,7 +34647,7 @@
         <v>185</v>
       </c>
       <c r="C3111" t="n">
-        <v>194.7834659631943</v>
+        <v>194.7834659631942</v>
       </c>
     </row>
     <row r="3112">
@@ -34658,7 +34658,7 @@
         <v>235</v>
       </c>
       <c r="C3112" t="n">
-        <v>211.0853735351788</v>
+        <v>211.0853735351787</v>
       </c>
     </row>
     <row r="3113">
@@ -34713,7 +34713,7 @@
         <v>418</v>
       </c>
       <c r="C3117" t="n">
-        <v>473.1549469829515</v>
+        <v>473.1549469829516</v>
       </c>
     </row>
     <row r="3118">
@@ -34801,7 +34801,7 @@
         <v>335</v>
       </c>
       <c r="C3125" t="n">
-        <v>324.1018054301659</v>
+        <v>324.101805430166</v>
       </c>
     </row>
     <row r="3126">
@@ -34867,7 +34867,7 @@
         <v>85</v>
       </c>
       <c r="C3131" t="n">
-        <v>88.93868061669168</v>
+        <v>88.93868061669171</v>
       </c>
     </row>
     <row r="3132">
@@ -34933,7 +34933,7 @@
         <v>590</v>
       </c>
       <c r="C3137" t="n">
-        <v>598.5889951201514</v>
+        <v>598.5889951201513</v>
       </c>
     </row>
     <row r="3138">
@@ -34944,7 +34944,7 @@
         <v>545</v>
       </c>
       <c r="C3138" t="n">
-        <v>597.3411622295512</v>
+        <v>597.3411622295511</v>
       </c>
     </row>
     <row r="3139">
@@ -34966,7 +34966,7 @@
         <v>522</v>
       </c>
       <c r="C3140" t="n">
-        <v>538.0611986534408</v>
+        <v>538.0611986534407</v>
       </c>
     </row>
     <row r="3141">
@@ -34977,7 +34977,7 @@
         <v>439</v>
       </c>
       <c r="C3141" t="n">
-        <v>551.9356212061833</v>
+        <v>551.9356212061834</v>
       </c>
     </row>
     <row r="3142">
@@ -35032,7 +35032,7 @@
         <v>450</v>
       </c>
       <c r="C3146" t="n">
-        <v>501.8530147582303</v>
+        <v>501.8530147582302</v>
       </c>
     </row>
     <row r="3147">
@@ -35098,7 +35098,7 @@
         <v>250</v>
       </c>
       <c r="C3152" t="n">
-        <v>191.5700890173215</v>
+        <v>191.5700890173216</v>
       </c>
     </row>
     <row r="3153">
@@ -35142,7 +35142,7 @@
         <v>113</v>
       </c>
       <c r="C3156" t="n">
-        <v>164.7263999264337</v>
+        <v>164.7263999264338</v>
       </c>
     </row>
     <row r="3157">
@@ -35197,7 +35197,7 @@
         <v>632</v>
       </c>
       <c r="C3161" t="n">
-        <v>603.272126018789</v>
+        <v>603.2721260187891</v>
       </c>
     </row>
     <row r="3162">
@@ -35230,7 +35230,7 @@
         <v>541</v>
       </c>
       <c r="C3164" t="n">
-        <v>559.4429016071904</v>
+        <v>559.4429016071905</v>
       </c>
     </row>
     <row r="3165">
@@ -35252,7 +35252,7 @@
         <v>405</v>
       </c>
       <c r="C3166" t="n">
-        <v>495.2487928596932</v>
+        <v>495.2487928596933</v>
       </c>
     </row>
     <row r="3167">
@@ -35263,7 +35263,7 @@
         <v>458</v>
       </c>
       <c r="C3167" t="n">
-        <v>440.713237622019</v>
+        <v>440.7132376220191</v>
       </c>
     </row>
     <row r="3168">
@@ -35318,7 +35318,7 @@
         <v>396</v>
       </c>
       <c r="C3172" t="n">
-        <v>430.9600273452714</v>
+        <v>430.9600273452715</v>
       </c>
     </row>
     <row r="3173">
@@ -35428,7 +35428,7 @@
         <v>286</v>
       </c>
       <c r="C3182" t="n">
-        <v>327.8326714450142</v>
+        <v>327.8326714450141</v>
       </c>
     </row>
     <row r="3183">
@@ -35483,7 +35483,7 @@
         <v>642</v>
       </c>
       <c r="C3187" t="n">
-        <v>573.9840573435996</v>
+        <v>573.9840573435997</v>
       </c>
     </row>
     <row r="3188">
@@ -35505,7 +35505,7 @@
         <v>447</v>
       </c>
       <c r="C3189" t="n">
-        <v>523.6946665365527</v>
+        <v>523.6946665365529</v>
       </c>
     </row>
     <row r="3190">
@@ -35560,7 +35560,7 @@
         <v>561</v>
       </c>
       <c r="C3194" t="n">
-        <v>507.6775971875555</v>
+        <v>507.6775971875554</v>
       </c>
     </row>
     <row r="3195">
@@ -35615,7 +35615,7 @@
         <v>324</v>
       </c>
       <c r="C3199" t="n">
-        <v>336.6831416146368</v>
+        <v>336.6831416146367</v>
       </c>
     </row>
     <row r="3200">
@@ -35703,7 +35703,7 @@
         <v>447</v>
       </c>
       <c r="C3207" t="n">
-        <v>457.2465868772764</v>
+        <v>457.2465868772765</v>
       </c>
     </row>
     <row r="3208">
@@ -35736,7 +35736,7 @@
         <v>539</v>
       </c>
       <c r="C3210" t="n">
-        <v>551.0800684180671</v>
+        <v>551.0800684180672</v>
       </c>
     </row>
     <row r="3211">
@@ -35769,7 +35769,7 @@
         <v>449</v>
       </c>
       <c r="C3213" t="n">
-        <v>506.6304208392179</v>
+        <v>506.630420839218</v>
       </c>
     </row>
     <row r="3214">
@@ -35813,7 +35813,7 @@
         <v>543</v>
       </c>
       <c r="C3217" t="n">
-        <v>508.6725701429424</v>
+        <v>508.6725701429423</v>
       </c>
     </row>
     <row r="3218">
@@ -36055,7 +36055,7 @@
         <v>431</v>
       </c>
       <c r="C3239" t="n">
-        <v>415.8384361309144</v>
+        <v>415.8384361309143</v>
       </c>
     </row>
     <row r="3240">
@@ -36077,7 +36077,7 @@
         <v>424</v>
       </c>
       <c r="C3241" t="n">
-        <v>437.8446904345128</v>
+        <v>437.8446904345126</v>
       </c>
     </row>
     <row r="3242">
@@ -36088,7 +36088,7 @@
         <v>440</v>
       </c>
       <c r="C3242" t="n">
-        <v>426.694289254449</v>
+        <v>426.6942892544491</v>
       </c>
     </row>
     <row r="3243">
@@ -36110,7 +36110,7 @@
         <v>409</v>
       </c>
       <c r="C3244" t="n">
-        <v>407.4468955677971</v>
+        <v>407.4468955677972</v>
       </c>
     </row>
     <row r="3245">
@@ -36253,7 +36253,7 @@
         <v>569</v>
       </c>
       <c r="C3257" t="n">
-        <v>584.7755545519359</v>
+        <v>584.775554551936</v>
       </c>
     </row>
     <row r="3258">
@@ -36286,7 +36286,7 @@
         <v>519</v>
       </c>
       <c r="C3260" t="n">
-        <v>595.7714349473914</v>
+        <v>595.7714349473915</v>
       </c>
     </row>
     <row r="3261">
@@ -36308,7 +36308,7 @@
         <v>474</v>
       </c>
       <c r="C3262" t="n">
-        <v>497.0066323102939</v>
+        <v>497.0066323102938</v>
       </c>
     </row>
     <row r="3263">
@@ -36319,7 +36319,7 @@
         <v>431</v>
       </c>
       <c r="C3263" t="n">
-        <v>469.2591242336308</v>
+        <v>469.2591242336309</v>
       </c>
     </row>
     <row r="3264">
@@ -36330,7 +36330,7 @@
         <v>434</v>
       </c>
       <c r="C3264" t="n">
-        <v>453.6679157303753</v>
+        <v>453.6679157303754</v>
       </c>
     </row>
     <row r="3265">
@@ -36363,7 +36363,7 @@
         <v>482</v>
       </c>
       <c r="C3267" t="n">
-        <v>461.5983581674618</v>
+        <v>461.5983581674617</v>
       </c>
     </row>
     <row r="3268">
@@ -36561,7 +36561,7 @@
         <v>452</v>
       </c>
       <c r="C3285" t="n">
-        <v>515.9196942058727</v>
+        <v>515.9196942058726</v>
       </c>
     </row>
     <row r="3286">
@@ -36616,7 +36616,7 @@
         <v>560</v>
       </c>
       <c r="C3290" t="n">
-        <v>517.0607511224767</v>
+        <v>517.0607511224766</v>
       </c>
     </row>
     <row r="3291">
@@ -36638,7 +36638,7 @@
         <v>367</v>
       </c>
       <c r="C3292" t="n">
-        <v>419.7886539788383</v>
+        <v>419.7886539788382</v>
       </c>
     </row>
     <row r="3293">
@@ -36671,7 +36671,7 @@
         <v>343</v>
       </c>
       <c r="C3295" t="n">
-        <v>313.7398614463026</v>
+        <v>313.7398614463025</v>
       </c>
     </row>
     <row r="3296">
@@ -36748,7 +36748,7 @@
         <v>400</v>
       </c>
       <c r="C3302" t="n">
-        <v>328.5537932677312</v>
+        <v>328.5537932677311</v>
       </c>
     </row>
     <row r="3303">
@@ -36803,7 +36803,7 @@
         <v>577</v>
       </c>
       <c r="C3307" t="n">
-        <v>564.4120972003144</v>
+        <v>564.4120972003145</v>
       </c>
     </row>
     <row r="3308">
@@ -36869,7 +36869,7 @@
         <v>489</v>
       </c>
       <c r="C3313" t="n">
-        <v>488.2832137509586</v>
+        <v>488.2832137509585</v>
       </c>
     </row>
     <row r="3314">
@@ -36913,7 +36913,7 @@
         <v>350</v>
       </c>
       <c r="C3317" t="n">
-        <v>382.4665736579407</v>
+        <v>382.4665736579408</v>
       </c>
     </row>
     <row r="3318">
@@ -37023,7 +37023,7 @@
         <v>472</v>
       </c>
       <c r="C3327" t="n">
-        <v>454.4789765325149</v>
+        <v>454.478976532515</v>
       </c>
     </row>
     <row r="3328">
@@ -37045,7 +37045,7 @@
         <v>534</v>
       </c>
       <c r="C3329" t="n">
-        <v>554.7730078001666</v>
+        <v>554.7730078001667</v>
       </c>
     </row>
     <row r="3330">
@@ -37089,7 +37089,7 @@
         <v>481</v>
       </c>
       <c r="C3333" t="n">
-        <v>518.0374565739155</v>
+        <v>518.0374565739156</v>
       </c>
     </row>
     <row r="3334">
@@ -37100,7 +37100,7 @@
         <v>489</v>
       </c>
       <c r="C3334" t="n">
-        <v>490.3294543863267</v>
+        <v>490.3294543863269</v>
       </c>
     </row>
     <row r="3335">
@@ -37122,7 +37122,7 @@
         <v>529</v>
       </c>
       <c r="C3336" t="n">
-        <v>470.7362770604474</v>
+        <v>470.7362770604475</v>
       </c>
     </row>
     <row r="3337">
@@ -37155,7 +37155,7 @@
         <v>604</v>
       </c>
       <c r="C3339" t="n">
-        <v>543.6295833526979</v>
+        <v>543.629583352698</v>
       </c>
     </row>
     <row r="3340">
@@ -37166,7 +37166,7 @@
         <v>569</v>
       </c>
       <c r="C3340" t="n">
-        <v>570.591329762054</v>
+        <v>570.5913297620541</v>
       </c>
     </row>
     <row r="3341">
@@ -37177,7 +37177,7 @@
         <v>482</v>
       </c>
       <c r="C3341" t="n">
-        <v>479.8346924332363</v>
+        <v>479.8346924332364</v>
       </c>
     </row>
     <row r="3342">
@@ -37188,7 +37188,7 @@
         <v>384</v>
       </c>
       <c r="C3342" t="n">
-        <v>432.1919350575804</v>
+        <v>432.1919350575803</v>
       </c>
     </row>
     <row r="3343">
@@ -37243,7 +37243,7 @@
         <v>310</v>
       </c>
       <c r="C3347" t="n">
-        <v>289.0104883652647</v>
+        <v>289.0104883652646</v>
       </c>
     </row>
     <row r="3348">
@@ -37353,7 +37353,7 @@
         <v>432</v>
       </c>
       <c r="C3357" t="n">
-        <v>418.0757185761185</v>
+        <v>418.0757185761186</v>
       </c>
     </row>
     <row r="3358">
@@ -37386,7 +37386,7 @@
         <v>451</v>
       </c>
       <c r="C3360" t="n">
-        <v>421.0429757994636</v>
+        <v>421.0429757994635</v>
       </c>
     </row>
     <row r="3361">
@@ -37474,7 +37474,7 @@
         <v>156</v>
       </c>
       <c r="C3368" t="n">
-        <v>164.0491594855501</v>
+        <v>164.04915948555</v>
       </c>
     </row>
     <row r="3369">
@@ -37507,7 +37507,7 @@
         <v>72</v>
       </c>
       <c r="C3371" t="n">
-        <v>87.83929481383288</v>
+        <v>87.83929481383285</v>
       </c>
     </row>
     <row r="3372">
@@ -37518,7 +37518,7 @@
         <v>88</v>
       </c>
       <c r="C3372" t="n">
-        <v>95.92427557913739</v>
+        <v>95.92427557913737</v>
       </c>
     </row>
     <row r="3373">
@@ -37584,7 +37584,7 @@
         <v>518</v>
       </c>
       <c r="C3378" t="n">
-        <v>521.4420224427903</v>
+        <v>521.4420224427904</v>
       </c>
     </row>
     <row r="3379">
@@ -37639,7 +37639,7 @@
         <v>389</v>
       </c>
       <c r="C3383" t="n">
-        <v>440.9274620417475</v>
+        <v>440.9274620417476</v>
       </c>
     </row>
     <row r="3384">
@@ -37661,7 +37661,7 @@
         <v>424</v>
       </c>
       <c r="C3385" t="n">
-        <v>450.6233644381231</v>
+        <v>450.6233644381232</v>
       </c>
     </row>
     <row r="3386">
@@ -37683,7 +37683,7 @@
         <v>375</v>
       </c>
       <c r="C3387" t="n">
-        <v>440.8905453968773</v>
+        <v>440.8905453968774</v>
       </c>
     </row>
     <row r="3388">
@@ -37815,7 +37815,7 @@
         <v>498</v>
       </c>
       <c r="C3399" t="n">
-        <v>515.4832194883239</v>
+        <v>515.483219488324</v>
       </c>
     </row>
     <row r="3400">
@@ -37870,7 +37870,7 @@
         <v>546</v>
       </c>
       <c r="C3404" t="n">
-        <v>556.5657050123958</v>
+        <v>556.5657050123959</v>
       </c>
     </row>
     <row r="3405">
@@ -37881,7 +37881,7 @@
         <v>446</v>
       </c>
       <c r="C3405" t="n">
-        <v>522.5475635990467</v>
+        <v>522.5475635990465</v>
       </c>
     </row>
     <row r="3406">
@@ -37892,7 +37892,7 @@
         <v>423</v>
       </c>
       <c r="C3406" t="n">
-        <v>455.3085284319584</v>
+        <v>455.3085284319583</v>
       </c>
     </row>
     <row r="3407">
@@ -37903,7 +37903,7 @@
         <v>441</v>
       </c>
       <c r="C3407" t="n">
-        <v>444.7221931323393</v>
+        <v>444.7221931323394</v>
       </c>
     </row>
     <row r="3408">
@@ -37925,7 +37925,7 @@
         <v>485</v>
       </c>
       <c r="C3409" t="n">
-        <v>489.0635860874329</v>
+        <v>489.0635860874328</v>
       </c>
     </row>
     <row r="3410">
@@ -37936,7 +37936,7 @@
         <v>452</v>
       </c>
       <c r="C3410" t="n">
-        <v>502.4382807240897</v>
+        <v>502.4382807240898</v>
       </c>
     </row>
     <row r="3411">
@@ -37947,7 +37947,7 @@
         <v>355</v>
       </c>
       <c r="C3411" t="n">
-        <v>466.2165314562404</v>
+        <v>466.2165314562403</v>
       </c>
     </row>
     <row r="3412">
@@ -38189,7 +38189,7 @@
         <v>416</v>
       </c>
       <c r="C3433" t="n">
-        <v>452.1680008290075</v>
+        <v>452.1680008290076</v>
       </c>
     </row>
     <row r="3434">
@@ -38200,7 +38200,7 @@
         <v>552</v>
       </c>
       <c r="C3434" t="n">
-        <v>460.1422593903644</v>
+        <v>460.1422593903642</v>
       </c>
     </row>
     <row r="3435">
@@ -38211,7 +38211,7 @@
         <v>503</v>
       </c>
       <c r="C3435" t="n">
-        <v>542.0956761666781</v>
+        <v>542.0956761666783</v>
       </c>
     </row>
     <row r="3436">
@@ -38233,7 +38233,7 @@
         <v>382</v>
       </c>
       <c r="C3437" t="n">
-        <v>377.1298016351648</v>
+        <v>377.1298016351649</v>
       </c>
     </row>
     <row r="3438">
@@ -38255,7 +38255,7 @@
         <v>327</v>
       </c>
       <c r="C3439" t="n">
-        <v>303.1898944881869</v>
+        <v>303.1898944881868</v>
       </c>
     </row>
     <row r="3440">
@@ -38354,7 +38354,7 @@
         <v>540</v>
       </c>
       <c r="C3448" t="n">
-        <v>552.6938895185881</v>
+        <v>552.693889518588</v>
       </c>
     </row>
     <row r="3449">
@@ -38365,7 +38365,7 @@
         <v>545</v>
       </c>
       <c r="C3449" t="n">
-        <v>559.2428649695726</v>
+        <v>559.2428649695725</v>
       </c>
     </row>
     <row r="3450">
@@ -38409,7 +38409,7 @@
         <v>436</v>
       </c>
       <c r="C3453" t="n">
-        <v>452.5331389337379</v>
+        <v>452.533138933738</v>
       </c>
     </row>
     <row r="3454">
@@ -38453,7 +38453,7 @@
         <v>498</v>
       </c>
       <c r="C3457" t="n">
-        <v>530.1644917202033</v>
+        <v>530.1644917202032</v>
       </c>
     </row>
     <row r="3458">
@@ -38475,7 +38475,7 @@
         <v>435</v>
       </c>
       <c r="C3459" t="n">
-        <v>440.0436843918121</v>
+        <v>440.0436843918122</v>
       </c>
     </row>
     <row r="3460">
@@ -38552,7 +38552,7 @@
         <v>332</v>
       </c>
       <c r="C3466" t="n">
-        <v>340.9965938650143</v>
+        <v>340.9965938650142</v>
       </c>
     </row>
     <row r="3467">
@@ -38695,7 +38695,7 @@
         <v>392</v>
       </c>
       <c r="C3479" t="n">
-        <v>410.915978038916</v>
+        <v>410.9159780389161</v>
       </c>
     </row>
     <row r="3480">
@@ -38717,7 +38717,7 @@
         <v>374</v>
       </c>
       <c r="C3481" t="n">
-        <v>423.3221925588293</v>
+        <v>423.3221925588292</v>
       </c>
     </row>
     <row r="3482">
@@ -38739,7 +38739,7 @@
         <v>341</v>
       </c>
       <c r="C3483" t="n">
-        <v>408.5648012978467</v>
+        <v>408.5648012978465</v>
       </c>
     </row>
     <row r="3484">
@@ -38761,7 +38761,7 @@
         <v>306</v>
       </c>
       <c r="C3485" t="n">
-        <v>303.3020991843229</v>
+        <v>303.3020991843228</v>
       </c>
     </row>
     <row r="3486">
@@ -38893,7 +38893,7 @@
         <v>609</v>
       </c>
       <c r="C3497" t="n">
-        <v>592.1471673418494</v>
+        <v>592.1471673418495</v>
       </c>
     </row>
     <row r="3498">
@@ -38904,7 +38904,7 @@
         <v>561</v>
       </c>
       <c r="C3498" t="n">
-        <v>592.1005833179369</v>
+        <v>592.100583317937</v>
       </c>
     </row>
     <row r="3499">
@@ -38915,7 +38915,7 @@
         <v>574</v>
       </c>
       <c r="C3499" t="n">
-        <v>579.7919926224376</v>
+        <v>579.7919926224375</v>
       </c>
     </row>
     <row r="3500">
@@ -38959,7 +38959,7 @@
         <v>414</v>
       </c>
       <c r="C3503" t="n">
-        <v>447.9095226374047</v>
+        <v>447.9095226374048</v>
       </c>
     </row>
     <row r="3504">
@@ -39047,7 +39047,7 @@
         <v>237</v>
       </c>
       <c r="C3511" t="n">
-        <v>234.9368375486007</v>
+        <v>234.9368375486006</v>
       </c>
     </row>
     <row r="3512">
@@ -39058,7 +39058,7 @@
         <v>227</v>
       </c>
       <c r="C3512" t="n">
-        <v>171.9306599185116</v>
+        <v>171.9306599185115</v>
       </c>
     </row>
     <row r="3513">
@@ -39124,7 +39124,7 @@
         <v>289</v>
       </c>
       <c r="C3518" t="n">
-        <v>346.994749549528</v>
+        <v>346.9947495495281</v>
       </c>
     </row>
     <row r="3519">
@@ -39168,7 +39168,7 @@
         <v>557</v>
       </c>
       <c r="C3522" t="n">
-        <v>575.6774769111478</v>
+        <v>575.6774769111479</v>
       </c>
     </row>
     <row r="3523">
@@ -39179,7 +39179,7 @@
         <v>599</v>
       </c>
       <c r="C3523" t="n">
-        <v>570.0675789210113</v>
+        <v>570.0675789210114</v>
       </c>
     </row>
     <row r="3524">
@@ -39201,7 +39201,7 @@
         <v>383</v>
       </c>
       <c r="C3525" t="n">
-        <v>514.5541074799255</v>
+        <v>514.5541074799254</v>
       </c>
     </row>
     <row r="3526">
@@ -39223,7 +39223,7 @@
         <v>430</v>
       </c>
       <c r="C3527" t="n">
-        <v>441.5777971787111</v>
+        <v>441.5777971787112</v>
       </c>
     </row>
     <row r="3528">
@@ -39454,7 +39454,7 @@
         <v>537</v>
       </c>
       <c r="C3548" t="n">
-        <v>530.5173081590971</v>
+        <v>530.517308159097</v>
       </c>
     </row>
     <row r="3549">
@@ -39564,7 +39564,7 @@
         <v>347</v>
       </c>
       <c r="C3558" t="n">
-        <v>337.8535766264178</v>
+        <v>337.8535766264179</v>
       </c>
     </row>
     <row r="3559">
@@ -39685,7 +39685,7 @@
         <v>593</v>
       </c>
       <c r="C3569" t="n">
-        <v>580.8238856428768</v>
+        <v>580.8238856428767</v>
       </c>
     </row>
     <row r="3570">
@@ -39707,7 +39707,7 @@
         <v>562</v>
       </c>
       <c r="C3571" t="n">
-        <v>567.0231235419483</v>
+        <v>567.0231235419484</v>
       </c>
     </row>
     <row r="3572">
@@ -39718,7 +39718,7 @@
         <v>516</v>
       </c>
       <c r="C3572" t="n">
-        <v>549.2594604773112</v>
+        <v>549.2594604773113</v>
       </c>
     </row>
     <row r="3573">
@@ -39729,7 +39729,7 @@
         <v>452</v>
       </c>
       <c r="C3573" t="n">
-        <v>507.1172963910803</v>
+        <v>507.1172963910802</v>
       </c>
     </row>
     <row r="3574">
@@ -39784,7 +39784,7 @@
         <v>527</v>
       </c>
       <c r="C3578" t="n">
-        <v>541.8114475323266</v>
+        <v>541.8114475323267</v>
       </c>
     </row>
     <row r="3579">
@@ -39795,7 +39795,7 @@
         <v>598</v>
       </c>
       <c r="C3579" t="n">
-        <v>554.3155689049224</v>
+        <v>554.3155689049223</v>
       </c>
     </row>
     <row r="3580">
@@ -39839,7 +39839,7 @@
         <v>307</v>
       </c>
       <c r="C3583" t="n">
-        <v>375.1427755362961</v>
+        <v>375.142775536296</v>
       </c>
     </row>
     <row r="3584">
@@ -39872,7 +39872,7 @@
         <v>317</v>
       </c>
       <c r="C3586" t="n">
-        <v>337.2205089542022</v>
+        <v>337.2205089542021</v>
       </c>
     </row>
     <row r="3587">
@@ -39982,7 +39982,7 @@
         <v>447</v>
       </c>
       <c r="C3596" t="n">
-        <v>438.4210415387439</v>
+        <v>438.421041538744</v>
       </c>
     </row>
     <row r="3597">
@@ -39993,7 +39993,7 @@
         <v>454</v>
       </c>
       <c r="C3597" t="n">
-        <v>452.053536260724</v>
+        <v>452.0535362607241</v>
       </c>
     </row>
     <row r="3598">
@@ -40015,7 +40015,7 @@
         <v>409</v>
       </c>
       <c r="C3599" t="n">
-        <v>408.9369689854747</v>
+        <v>408.9369689854746</v>
       </c>
     </row>
     <row r="3600">
@@ -40059,7 +40059,7 @@
         <v>324</v>
       </c>
       <c r="C3603" t="n">
-        <v>421.4606246887399</v>
+        <v>421.4606246887398</v>
       </c>
     </row>
     <row r="3604">
@@ -40378,7 +40378,7 @@
         <v>263</v>
       </c>
       <c r="C3632" t="n">
-        <v>186.2197850233918</v>
+        <v>186.2197850233919</v>
       </c>
     </row>
     <row r="3633">
@@ -40477,7 +40477,7 @@
         <v>582</v>
       </c>
       <c r="C3641" t="n">
-        <v>576.4975405294419</v>
+        <v>576.4975405294418</v>
       </c>
     </row>
     <row r="3642">
@@ -40521,7 +40521,7 @@
         <v>428</v>
       </c>
       <c r="C3645" t="n">
-        <v>502.7655104653037</v>
+        <v>502.7655104653038</v>
       </c>
     </row>
     <row r="3646">
@@ -40532,7 +40532,7 @@
         <v>428</v>
       </c>
       <c r="C3646" t="n">
-        <v>421.3934498043168</v>
+        <v>421.3934498043169</v>
       </c>
     </row>
     <row r="3647">
@@ -40631,7 +40631,7 @@
         <v>352</v>
       </c>
       <c r="C3655" t="n">
-        <v>288.1740801889788</v>
+        <v>288.1740801889787</v>
       </c>
     </row>
     <row r="3656">
@@ -40675,7 +40675,7 @@
         <v>195</v>
       </c>
       <c r="C3659" t="n">
-        <v>193.3695284136258</v>
+        <v>193.3695284136259</v>
       </c>
     </row>
     <row r="3660">
@@ -40719,7 +40719,7 @@
         <v>524</v>
       </c>
       <c r="C3663" t="n">
-        <v>472.1724109912221</v>
+        <v>472.172410991222</v>
       </c>
     </row>
     <row r="3664">
@@ -40741,7 +40741,7 @@
         <v>575</v>
       </c>
       <c r="C3665" t="n">
-        <v>578.5805348858033</v>
+        <v>578.5805348858032</v>
       </c>
     </row>
     <row r="3666">
@@ -40752,7 +40752,7 @@
         <v>573</v>
       </c>
       <c r="C3666" t="n">
-        <v>537.1038393414158</v>
+        <v>537.1038393414159</v>
       </c>
     </row>
     <row r="3667">
@@ -40785,7 +40785,7 @@
         <v>440</v>
       </c>
       <c r="C3669" t="n">
-        <v>493.1144259122727</v>
+        <v>493.1144259122728</v>
       </c>
     </row>
     <row r="3670">
@@ -40840,7 +40840,7 @@
         <v>569</v>
       </c>
       <c r="C3674" t="n">
-        <v>459.5463555662167</v>
+        <v>459.5463555662166</v>
       </c>
     </row>
     <row r="3675">
@@ -40862,7 +40862,7 @@
         <v>419</v>
       </c>
       <c r="C3676" t="n">
-        <v>405.8195817918014</v>
+        <v>405.8195817918015</v>
       </c>
     </row>
     <row r="3677">
@@ -40994,7 +40994,7 @@
         <v>528</v>
       </c>
       <c r="C3688" t="n">
-        <v>484.8153063626945</v>
+        <v>484.8153063626944</v>
       </c>
     </row>
     <row r="3689">
@@ -41005,7 +41005,7 @@
         <v>500</v>
       </c>
       <c r="C3689" t="n">
-        <v>512.9465204870044</v>
+        <v>512.9465204870045</v>
       </c>
     </row>
     <row r="3690">
@@ -41016,7 +41016,7 @@
         <v>527</v>
       </c>
       <c r="C3690" t="n">
-        <v>510.7022214639209</v>
+        <v>510.702221463921</v>
       </c>
     </row>
     <row r="3691">
@@ -41049,7 +41049,7 @@
         <v>467</v>
       </c>
       <c r="C3693" t="n">
-        <v>445.4164689973778</v>
+        <v>445.4164689973776</v>
       </c>
     </row>
     <row r="3694">
@@ -41093,7 +41093,7 @@
         <v>494</v>
       </c>
       <c r="C3697" t="n">
-        <v>423.8474678158336</v>
+        <v>423.8474678158335</v>
       </c>
     </row>
     <row r="3698">
@@ -41104,7 +41104,7 @@
         <v>459</v>
       </c>
       <c r="C3698" t="n">
-        <v>483.6865294748748</v>
+        <v>483.6865294748749</v>
       </c>
     </row>
     <row r="3699">
@@ -41148,7 +41148,7 @@
         <v>354</v>
       </c>
       <c r="C3702" t="n">
-        <v>328.5043394760473</v>
+        <v>328.5043394760474</v>
       </c>
     </row>
     <row r="3703">
@@ -41170,7 +41170,7 @@
         <v>449</v>
       </c>
       <c r="C3704" t="n">
-        <v>339.6013398114948</v>
+        <v>339.6013398114949</v>
       </c>
     </row>
     <row r="3705">
@@ -41236,7 +41236,7 @@
         <v>222</v>
       </c>
       <c r="C3710" t="n">
-        <v>197.2910138025942</v>
+        <v>197.2910138025943</v>
       </c>
     </row>
     <row r="3711">
@@ -41313,7 +41313,7 @@
         <v>504</v>
       </c>
       <c r="C3717" t="n">
-        <v>388.771312371551</v>
+        <v>388.7713123715511</v>
       </c>
     </row>
     <row r="3718">
@@ -41335,7 +41335,7 @@
         <v>438</v>
       </c>
       <c r="C3719" t="n">
-        <v>409.2363909781255</v>
+        <v>409.2363909781254</v>
       </c>
     </row>
     <row r="3720">
@@ -41346,7 +41346,7 @@
         <v>421</v>
       </c>
       <c r="C3720" t="n">
-        <v>421.7776234668689</v>
+        <v>421.777623466869</v>
       </c>
     </row>
     <row r="3721">
@@ -41368,7 +41368,7 @@
         <v>403</v>
       </c>
       <c r="C3722" t="n">
-        <v>425.3479383057469</v>
+        <v>425.347938305747</v>
       </c>
     </row>
     <row r="3723">
@@ -41401,7 +41401,7 @@
         <v>299</v>
       </c>
       <c r="C3725" t="n">
-        <v>298.2042117480968</v>
+        <v>298.2042117480967</v>
       </c>
     </row>
     <row r="3726">
@@ -41412,7 +41412,7 @@
         <v>259</v>
       </c>
       <c r="C3726" t="n">
-        <v>262.0173932189193</v>
+        <v>262.0173932189194</v>
       </c>
     </row>
     <row r="3727">
@@ -41434,7 +41434,7 @@
         <v>202</v>
       </c>
       <c r="C3728" t="n">
-        <v>169.048298940852</v>
+        <v>169.0482989408521</v>
       </c>
     </row>
     <row r="3729">
@@ -41522,7 +41522,7 @@
         <v>523</v>
       </c>
       <c r="C3736" t="n">
-        <v>592.2154454550242</v>
+        <v>592.2154454550243</v>
       </c>
     </row>
     <row r="3737">
@@ -41588,7 +41588,7 @@
         <v>440</v>
       </c>
       <c r="C3742" t="n">
-        <v>440.3900861956278</v>
+        <v>440.3900861956279</v>
       </c>
     </row>
     <row r="3743">
@@ -41610,7 +41610,7 @@
         <v>445</v>
       </c>
       <c r="C3744" t="n">
-        <v>423.6068307803677</v>
+        <v>423.6068307803676</v>
       </c>
     </row>
     <row r="3745">
@@ -41621,7 +41621,7 @@
         <v>531</v>
       </c>
       <c r="C3745" t="n">
-        <v>441.0362557008743</v>
+        <v>441.0362557008744</v>
       </c>
     </row>
     <row r="3746">
@@ -41643,7 +41643,7 @@
         <v>360</v>
       </c>
       <c r="C3747" t="n">
-        <v>455.1405752847282</v>
+        <v>455.1405752847281</v>
       </c>
     </row>
     <row r="3748">
@@ -41698,7 +41698,7 @@
         <v>263</v>
       </c>
       <c r="C3752" t="n">
-        <v>181.730827032006</v>
+        <v>181.7308270320059</v>
       </c>
     </row>
     <row r="3753">
@@ -41764,7 +41764,7 @@
         <v>336</v>
       </c>
       <c r="C3758" t="n">
-        <v>328.7323351743325</v>
+        <v>328.7323351743324</v>
       </c>
     </row>
     <row r="3759">
@@ -41775,7 +41775,7 @@
         <v>496</v>
       </c>
       <c r="C3759" t="n">
-        <v>487.6709462567058</v>
+        <v>487.6709462567057</v>
       </c>
     </row>
     <row r="3760">
@@ -41819,7 +41819,7 @@
         <v>592</v>
       </c>
       <c r="C3763" t="n">
-        <v>532.8704444922829</v>
+        <v>532.870444492283</v>
       </c>
     </row>
     <row r="3764">
@@ -41896,7 +41896,7 @@
         <v>589</v>
       </c>
       <c r="C3770" t="n">
-        <v>455.8298890003504</v>
+        <v>455.8298890003505</v>
       </c>
     </row>
     <row r="3771">
@@ -41918,7 +41918,7 @@
         <v>391</v>
       </c>
       <c r="C3772" t="n">
-        <v>437.3871350495346</v>
+        <v>437.3871350495345</v>
       </c>
     </row>
     <row r="3773">
@@ -41929,7 +41929,7 @@
         <v>332</v>
       </c>
       <c r="C3773" t="n">
-        <v>335.9911831375604</v>
+        <v>335.9911831375605</v>
       </c>
     </row>
     <row r="3774">
@@ -42050,7 +42050,7 @@
         <v>580</v>
       </c>
       <c r="C3784" t="n">
-        <v>535.3280352369628</v>
+        <v>535.3280352369629</v>
       </c>
     </row>
     <row r="3785">
@@ -42127,7 +42127,7 @@
         <v>407</v>
       </c>
       <c r="C3791" t="n">
-        <v>443.0761843640649</v>
+        <v>443.0761843640648</v>
       </c>
     </row>
     <row r="3792">
@@ -42160,7 +42160,7 @@
         <v>486</v>
       </c>
       <c r="C3794" t="n">
-        <v>461.2293377600868</v>
+        <v>461.2293377600867</v>
       </c>
     </row>
     <row r="3795">
@@ -42182,7 +42182,7 @@
         <v>426</v>
       </c>
       <c r="C3796" t="n">
-        <v>430.8595078247303</v>
+        <v>430.8595078247304</v>
       </c>
     </row>
     <row r="3797">
@@ -42259,7 +42259,7 @@
         <v>208</v>
       </c>
       <c r="C3803" t="n">
-        <v>203.0971361302279</v>
+        <v>203.0971361302278</v>
       </c>
     </row>
     <row r="3804">
@@ -42325,7 +42325,7 @@
         <v>567</v>
       </c>
       <c r="C3809" t="n">
-        <v>526.5799219251902</v>
+        <v>526.5799219251901</v>
       </c>
     </row>
     <row r="3810">
@@ -42380,7 +42380,7 @@
         <v>407</v>
       </c>
       <c r="C3814" t="n">
-        <v>448.4266104919545</v>
+        <v>448.4266104919544</v>
       </c>
     </row>
     <row r="3815">
@@ -42446,7 +42446,7 @@
         <v>543</v>
       </c>
       <c r="C3820" t="n">
-        <v>483.2804679455224</v>
+        <v>483.2804679455223</v>
       </c>
     </row>
     <row r="3821">
@@ -42468,7 +42468,7 @@
         <v>427</v>
       </c>
       <c r="C3822" t="n">
-        <v>375.3871599233751</v>
+        <v>375.3871599233752</v>
       </c>
     </row>
     <row r="3823">
@@ -42512,7 +42512,7 @@
         <v>324</v>
       </c>
       <c r="C3826" t="n">
-        <v>137.490888255147</v>
+        <v>137.4908882551471</v>
       </c>
     </row>
     <row r="3827">
@@ -42523,7 +42523,7 @@
         <v>302</v>
       </c>
       <c r="C3827" t="n">
-        <v>296.0621704319627</v>
+        <v>296.0621704319628</v>
       </c>
     </row>
     <row r="3828">
@@ -42622,7 +42622,7 @@
         <v>398</v>
       </c>
       <c r="C3836" t="n">
-        <v>408.4773341300552</v>
+        <v>408.4773341300551</v>
       </c>
     </row>
     <row r="3837">
@@ -42677,7 +42677,7 @@
         <v>437</v>
       </c>
       <c r="C3841" t="n">
-        <v>411.7696551117769</v>
+        <v>411.769655111777</v>
       </c>
     </row>
     <row r="3842">
@@ -42721,7 +42721,7 @@
         <v>353</v>
       </c>
       <c r="C3845" t="n">
-        <v>330.8461766397093</v>
+        <v>330.8461766397094</v>
       </c>
     </row>
     <row r="3846">
